--- a/demo_data/sectors/hizmet_yazilim/sales_ledger.xlsx
+++ b/demo_data/sectors/hizmet_yazilim/sales_ledger.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Maliyet</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Net Satış Tutarı</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Maliyet</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -492,37 +492,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F2" t="n">
-        <v>38406.91</v>
+        <v>56899.06</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1609.47</v>
       </c>
       <c r="H2" t="n">
-        <v>38406.91</v>
+        <v>35561.87</v>
       </c>
       <c r="I2" t="n">
-        <v>26244.72</v>
+        <v>55289.59</v>
       </c>
       <c r="J2" t="n">
-        <v>38406.91</v>
+        <v>55289.59</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -536,32 +536,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F3" t="n">
-        <v>369666.55</v>
+        <v>56042.87</v>
       </c>
       <c r="G3" t="n">
-        <v>29573.32</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>340093.23</v>
+        <v>37866.8</v>
       </c>
       <c r="I3" t="n">
-        <v>235242.35</v>
+        <v>56042.87</v>
       </c>
       <c r="J3" t="n">
-        <v>340093.23</v>
+        <v>56042.87</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,37 +570,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>45662</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F4" t="n">
-        <v>32005.76</v>
+        <v>396448.98</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>7476.02</v>
       </c>
       <c r="H4" t="n">
-        <v>32005.76</v>
+        <v>261840.72</v>
       </c>
       <c r="I4" t="n">
-        <v>20003.6</v>
+        <v>388972.96</v>
       </c>
       <c r="J4" t="n">
-        <v>32005.76</v>
+        <v>388972.96</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,37 +609,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F5" t="n">
-        <v>6934.58</v>
+        <v>94041.39</v>
       </c>
       <c r="G5" t="n">
-        <v>346.73</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6587.85</v>
+        <v>62694.26</v>
       </c>
       <c r="I5" t="n">
-        <v>4694.18</v>
+        <v>94041.39</v>
       </c>
       <c r="J5" t="n">
-        <v>6587.85</v>
+        <v>94041.39</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,7 +648,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -660,25 +660,25 @@
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
         <v>1200</v>
       </c>
       <c r="F6" t="n">
-        <v>25604.61</v>
+        <v>36352.13</v>
       </c>
       <c r="G6" t="n">
-        <v>2048.37</v>
+        <v>1713.77</v>
       </c>
       <c r="H6" t="n">
-        <v>23556.24</v>
+        <v>24840.62</v>
       </c>
       <c r="I6" t="n">
-        <v>17496.48</v>
+        <v>34638.36</v>
       </c>
       <c r="J6" t="n">
-        <v>23556.24</v>
+        <v>34638.36</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F7" t="n">
-        <v>7801.4</v>
+        <v>40566.87</v>
       </c>
       <c r="G7" t="n">
-        <v>390.07</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>7411.33</v>
+        <v>25815.28</v>
       </c>
       <c r="I7" t="n">
-        <v>5280.95</v>
+        <v>40566.87</v>
       </c>
       <c r="J7" t="n">
-        <v>7411.33</v>
+        <v>40566.87</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,37 +726,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F8" t="n">
-        <v>430077.43</v>
+        <v>365101.85</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>17212.24</v>
       </c>
       <c r="H8" t="n">
-        <v>430077.43</v>
+        <v>232337.54</v>
       </c>
       <c r="I8" t="n">
-        <v>284051.14</v>
+        <v>347889.61</v>
       </c>
       <c r="J8" t="n">
-        <v>430077.43</v>
+        <v>347889.61</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,12 +765,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -780,22 +780,22 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F9" t="n">
-        <v>5200.94</v>
+        <v>14619.88</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>275.69</v>
       </c>
       <c r="H9" t="n">
-        <v>5200.94</v>
+        <v>9878.299999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>3520.63</v>
+        <v>14344.19</v>
       </c>
       <c r="J9" t="n">
-        <v>5200.94</v>
+        <v>14344.19</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,37 +804,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F10" t="n">
-        <v>172030.97</v>
+        <v>30030.02</v>
       </c>
       <c r="G10" t="n">
-        <v>13762.48</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>158268.49</v>
+        <v>20520.52</v>
       </c>
       <c r="I10" t="n">
-        <v>113620.46</v>
+        <v>30030.02</v>
       </c>
       <c r="J10" t="n">
-        <v>158268.49</v>
+        <v>30030.02</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F11" t="n">
-        <v>41940.88</v>
+        <v>9483.16</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.83</v>
       </c>
       <c r="H11" t="n">
-        <v>41940.88</v>
+        <v>5926.98</v>
       </c>
       <c r="I11" t="n">
-        <v>28338.44</v>
+        <v>9304.33</v>
       </c>
       <c r="J11" t="n">
-        <v>41940.88</v>
+        <v>9304.33</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -882,37 +882,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="F12" t="n">
-        <v>123222.18</v>
+        <v>30030.02</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>849.4400000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>123222.18</v>
+        <v>20520.52</v>
       </c>
       <c r="I12" t="n">
-        <v>82148.12</v>
+        <v>29180.58</v>
       </c>
       <c r="J12" t="n">
-        <v>123222.18</v>
+        <v>29180.58</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -921,37 +921,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F13" t="n">
-        <v>34539.55</v>
+        <v>11129.55</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>34539.55</v>
+        <v>7533.85</v>
       </c>
       <c r="I13" t="n">
-        <v>23337.53</v>
+        <v>11129.55</v>
       </c>
       <c r="J13" t="n">
-        <v>34539.55</v>
+        <v>11129.55</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,37 +960,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F14" t="n">
-        <v>4800.86</v>
+        <v>94041.39</v>
       </c>
       <c r="G14" t="n">
-        <v>576.1</v>
+        <v>1773.38</v>
       </c>
       <c r="H14" t="n">
-        <v>4224.76</v>
+        <v>62694.26</v>
       </c>
       <c r="I14" t="n">
-        <v>3280.59</v>
+        <v>92268.00999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>4224.76</v>
+        <v>92268.00999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F15" t="n">
-        <v>17269.78</v>
+        <v>77445.85000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1381.58</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>15888.19</v>
+        <v>51630.56</v>
       </c>
       <c r="I15" t="n">
-        <v>11668.77</v>
+        <v>77445.85000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>15888.19</v>
+        <v>77445.85000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F16" t="n">
-        <v>1733.65</v>
+        <v>60850.31</v>
       </c>
       <c r="G16" t="n">
-        <v>138.69</v>
+        <v>2868.71</v>
       </c>
       <c r="H16" t="n">
-        <v>1594.95</v>
+        <v>40566.87</v>
       </c>
       <c r="I16" t="n">
-        <v>1173.54</v>
+        <v>57981.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1594.95</v>
+        <v>57981.6</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F17" t="n">
-        <v>630780.23</v>
+        <v>79026.37</v>
       </c>
       <c r="G17" t="n">
-        <v>31539.01</v>
+        <v>1490.24</v>
       </c>
       <c r="H17" t="n">
-        <v>599241.21</v>
+        <v>49391.48</v>
       </c>
       <c r="I17" t="n">
-        <v>416608.34</v>
+        <v>77536.13</v>
       </c>
       <c r="J17" t="n">
-        <v>599241.21</v>
+        <v>77536.13</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E18" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F18" t="n">
-        <v>44407.99</v>
+        <v>304251.54</v>
       </c>
       <c r="G18" t="n">
-        <v>3552.64</v>
+        <v>8606.120000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>40855.36</v>
+        <v>193614.62</v>
       </c>
       <c r="I18" t="n">
-        <v>30005.4</v>
+        <v>295645.42</v>
       </c>
       <c r="J18" t="n">
-        <v>40855.36</v>
+        <v>295645.42</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,37 +1155,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F19" t="n">
-        <v>2467.11</v>
+        <v>15410.14</v>
       </c>
       <c r="G19" t="n">
-        <v>197.37</v>
+        <v>435.89</v>
       </c>
       <c r="H19" t="n">
-        <v>2269.74</v>
+        <v>10431.48</v>
       </c>
       <c r="I19" t="n">
-        <v>1666.97</v>
+        <v>14974.25</v>
       </c>
       <c r="J19" t="n">
-        <v>2269.74</v>
+        <v>14974.25</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E20" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F20" t="n">
-        <v>369666.55</v>
+        <v>257889.4</v>
       </c>
       <c r="G20" t="n">
-        <v>11090</v>
+        <v>12157.85</v>
       </c>
       <c r="H20" t="n">
-        <v>358576.55</v>
+        <v>170960.39</v>
       </c>
       <c r="I20" t="n">
-        <v>235242.35</v>
+        <v>245731.55</v>
       </c>
       <c r="J20" t="n">
-        <v>358576.55</v>
+        <v>245731.55</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1245,25 +1245,25 @@
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>2400</v>
       </c>
       <c r="F21" t="n">
-        <v>19203.46</v>
+        <v>9483.16</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>447.07</v>
       </c>
       <c r="H21" t="n">
-        <v>19203.46</v>
+        <v>5926.98</v>
       </c>
       <c r="I21" t="n">
-        <v>12002.16</v>
+        <v>9036.09</v>
       </c>
       <c r="J21" t="n">
-        <v>19203.46</v>
+        <v>9036.09</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="F22" t="n">
-        <v>95217.14</v>
+        <v>36352.13</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>95217.14</v>
+        <v>24840.62</v>
       </c>
       <c r="I22" t="n">
-        <v>63478.09</v>
+        <v>36352.13</v>
       </c>
       <c r="J22" t="n">
-        <v>95217.14</v>
+        <v>36352.13</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>1200</v>
+        <v>15400</v>
       </c>
       <c r="F23" t="n">
-        <v>32005.76</v>
+        <v>101417.18</v>
       </c>
       <c r="G23" t="n">
-        <v>2560.46</v>
+        <v>2868.71</v>
       </c>
       <c r="H23" t="n">
-        <v>29445.3</v>
+        <v>64538.21</v>
       </c>
       <c r="I23" t="n">
-        <v>21870.6</v>
+        <v>98548.47</v>
       </c>
       <c r="J23" t="n">
-        <v>29445.3</v>
+        <v>98548.47</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F24" t="n">
-        <v>7801.4</v>
+        <v>281333.89</v>
       </c>
       <c r="G24" t="n">
-        <v>390.07</v>
+        <v>7957.87</v>
       </c>
       <c r="H24" t="n">
-        <v>7411.33</v>
+        <v>186502.24</v>
       </c>
       <c r="I24" t="n">
-        <v>5280.95</v>
+        <v>273376.02</v>
       </c>
       <c r="J24" t="n">
-        <v>7411.33</v>
+        <v>273376.02</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,7 +1389,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1401,25 +1401,25 @@
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>650</v>
       </c>
       <c r="F25" t="n">
-        <v>11268.7</v>
+        <v>3424.48</v>
       </c>
       <c r="G25" t="n">
-        <v>563.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>10705.26</v>
+        <v>2318.11</v>
       </c>
       <c r="I25" t="n">
-        <v>7628.04</v>
+        <v>3424.48</v>
       </c>
       <c r="J25" t="n">
-        <v>10705.26</v>
+        <v>3424.48</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>1200</v>
+        <v>15400</v>
       </c>
       <c r="F26" t="n">
-        <v>36806.63</v>
+        <v>304251.54</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5737.41</v>
       </c>
       <c r="H26" t="n">
-        <v>36806.63</v>
+        <v>193614.62</v>
       </c>
       <c r="I26" t="n">
-        <v>25151.19</v>
+        <v>298514.13</v>
       </c>
       <c r="J26" t="n">
-        <v>36806.63</v>
+        <v>298514.13</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F27" t="n">
-        <v>117621.18</v>
+        <v>81133.74000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>14114.54</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>103506.63</v>
+        <v>51630.56</v>
       </c>
       <c r="I27" t="n">
-        <v>78414.12</v>
+        <v>81133.74000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>103506.63</v>
+        <v>81133.74000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F28" t="n">
-        <v>7401.33</v>
+        <v>164111.44</v>
       </c>
       <c r="G28" t="n">
-        <v>370.07</v>
+        <v>4642.09</v>
       </c>
       <c r="H28" t="n">
-        <v>7031.27</v>
+        <v>108792.98</v>
       </c>
       <c r="I28" t="n">
-        <v>5000.9</v>
+        <v>159469.35</v>
       </c>
       <c r="J28" t="n">
-        <v>7031.27</v>
+        <v>159469.35</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1557,25 +1557,25 @@
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
         <v>2400</v>
       </c>
       <c r="F29" t="n">
-        <v>57610.37</v>
+        <v>12644.22</v>
       </c>
       <c r="G29" t="n">
-        <v>2880.52</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>54729.85</v>
+        <v>7902.64</v>
       </c>
       <c r="I29" t="n">
-        <v>36006.48</v>
+        <v>12644.22</v>
       </c>
       <c r="J29" t="n">
-        <v>54729.85</v>
+        <v>12644.22</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F30" t="n">
-        <v>56743.55</v>
+        <v>15410.14</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>56743.55</v>
+        <v>10431.48</v>
       </c>
       <c r="I30" t="n">
-        <v>38340.24</v>
+        <v>15410.14</v>
       </c>
       <c r="J30" t="n">
-        <v>56743.55</v>
+        <v>15410.14</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F31" t="n">
-        <v>401405.6</v>
+        <v>11129.55</v>
       </c>
       <c r="G31" t="n">
-        <v>48168.67</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>353236.93</v>
+        <v>7533.85</v>
       </c>
       <c r="I31" t="n">
-        <v>265114.4</v>
+        <v>11129.55</v>
       </c>
       <c r="J31" t="n">
-        <v>353236.93</v>
+        <v>11129.55</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F32" t="n">
-        <v>16469.63</v>
+        <v>41093.71</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>16469.63</v>
+        <v>25683.57</v>
       </c>
       <c r="I32" t="n">
-        <v>11148.67</v>
+        <v>41093.71</v>
       </c>
       <c r="J32" t="n">
-        <v>16469.63</v>
+        <v>41093.71</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F33" t="n">
-        <v>19736.89</v>
+        <v>30030.02</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1415.73</v>
       </c>
       <c r="H33" t="n">
-        <v>19736.89</v>
+        <v>20520.52</v>
       </c>
       <c r="I33" t="n">
-        <v>13335.73</v>
+        <v>28614.29</v>
       </c>
       <c r="J33" t="n">
-        <v>19736.89</v>
+        <v>28614.29</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F34" t="n">
-        <v>258046.46</v>
+        <v>18966.33</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>258046.46</v>
+        <v>11853.96</v>
       </c>
       <c r="I34" t="n">
-        <v>170430.68</v>
+        <v>18966.33</v>
       </c>
       <c r="J34" t="n">
-        <v>258046.46</v>
+        <v>18966.33</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,37 +1779,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F35" t="n">
-        <v>123222.18</v>
+        <v>182550.92</v>
       </c>
       <c r="G35" t="n">
-        <v>3696.67</v>
+        <v>5163.67</v>
       </c>
       <c r="H35" t="n">
-        <v>119525.52</v>
+        <v>116168.77</v>
       </c>
       <c r="I35" t="n">
-        <v>82148.12</v>
+        <v>177387.25</v>
       </c>
       <c r="J35" t="n">
-        <v>119525.52</v>
+        <v>177387.25</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,12 +1818,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1833,22 +1833,22 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F36" t="n">
-        <v>14802.66</v>
+        <v>33191.08</v>
       </c>
       <c r="G36" t="n">
-        <v>444.08</v>
+        <v>938.85</v>
       </c>
       <c r="H36" t="n">
-        <v>14358.58</v>
+        <v>22127.38</v>
       </c>
       <c r="I36" t="n">
-        <v>10001.8</v>
+        <v>32252.23</v>
       </c>
       <c r="J36" t="n">
-        <v>14358.58</v>
+        <v>32252.23</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,37 +1857,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F37" t="n">
-        <v>30405.47</v>
+        <v>31610.55</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>894.14</v>
       </c>
       <c r="H37" t="n">
-        <v>30405.47</v>
+        <v>19756.59</v>
       </c>
       <c r="I37" t="n">
-        <v>20777.07</v>
+        <v>30716.41</v>
       </c>
       <c r="J37" t="n">
-        <v>30405.47</v>
+        <v>30716.41</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1901,32 +1901,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F38" t="n">
-        <v>9601.73</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>288.05</v>
+        <v>1251.8</v>
       </c>
       <c r="H38" t="n">
-        <v>9313.68</v>
+        <v>44254.77</v>
       </c>
       <c r="I38" t="n">
-        <v>6001.08</v>
+        <v>65130.35</v>
       </c>
       <c r="J38" t="n">
-        <v>9313.68</v>
+        <v>65130.35</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E39" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F39" t="n">
-        <v>30405.47</v>
+        <v>566355.6800000001</v>
       </c>
       <c r="G39" t="n">
-        <v>1520.27</v>
+        <v>26700.08</v>
       </c>
       <c r="H39" t="n">
-        <v>28885.2</v>
+        <v>374058.17</v>
       </c>
       <c r="I39" t="n">
-        <v>20777.07</v>
+        <v>539655.6</v>
       </c>
       <c r="J39" t="n">
-        <v>28885.2</v>
+        <v>539655.6</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F40" t="n">
-        <v>11268.7</v>
+        <v>113271.14</v>
       </c>
       <c r="G40" t="n">
-        <v>1352.24</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>9916.450000000001</v>
+        <v>74811.63</v>
       </c>
       <c r="I40" t="n">
-        <v>7628.04</v>
+        <v>113271.14</v>
       </c>
       <c r="J40" t="n">
-        <v>9916.450000000001</v>
+        <v>113271.14</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F41" t="n">
-        <v>95217.14</v>
+        <v>31676.41</v>
       </c>
       <c r="G41" t="n">
-        <v>11426.06</v>
+        <v>597.34</v>
       </c>
       <c r="H41" t="n">
-        <v>83791.08</v>
+        <v>21402.98</v>
       </c>
       <c r="I41" t="n">
-        <v>63478.09</v>
+        <v>31079.07</v>
       </c>
       <c r="J41" t="n">
-        <v>83791.08</v>
+        <v>31079.07</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F42" t="n">
-        <v>9868.440000000001</v>
+        <v>34771.6</v>
       </c>
       <c r="G42" t="n">
-        <v>493.42</v>
+        <v>983.5599999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>9375.02</v>
+        <v>21732.25</v>
       </c>
       <c r="I42" t="n">
-        <v>6667.87</v>
+        <v>33788.04</v>
       </c>
       <c r="J42" t="n">
-        <v>9375.02</v>
+        <v>33788.04</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E43" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F43" t="n">
-        <v>61611.09</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>4928.89</v>
+        <v>3129.5</v>
       </c>
       <c r="H43" t="n">
-        <v>56682.2</v>
+        <v>41488.85</v>
       </c>
       <c r="I43" t="n">
-        <v>41074.06</v>
+        <v>63252.65</v>
       </c>
       <c r="J43" t="n">
-        <v>56682.2</v>
+        <v>63252.65</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E44" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F44" t="n">
-        <v>80014.41</v>
+        <v>223117.8</v>
       </c>
       <c r="G44" t="n">
-        <v>2400.43</v>
+        <v>10518.59</v>
       </c>
       <c r="H44" t="n">
-        <v>77613.97</v>
+        <v>141984.05</v>
       </c>
       <c r="I44" t="n">
-        <v>50009</v>
+        <v>212599.21</v>
       </c>
       <c r="J44" t="n">
-        <v>77613.97</v>
+        <v>212599.21</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,37 +2169,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>15400</v>
+        <v>1200</v>
       </c>
       <c r="F45" t="n">
-        <v>308055.46</v>
+        <v>25288.44</v>
       </c>
       <c r="G45" t="n">
-        <v>15402.77</v>
+        <v>476.88</v>
       </c>
       <c r="H45" t="n">
-        <v>292652.69</v>
+        <v>17280.43</v>
       </c>
       <c r="I45" t="n">
-        <v>196035.29</v>
+        <v>24811.56</v>
       </c>
       <c r="J45" t="n">
-        <v>292652.69</v>
+        <v>24811.56</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F46" t="n">
-        <v>15602.81</v>
+        <v>34771.6</v>
       </c>
       <c r="G46" t="n">
-        <v>780.14</v>
+        <v>655.7</v>
       </c>
       <c r="H46" t="n">
-        <v>14822.67</v>
+        <v>21732.25</v>
       </c>
       <c r="I46" t="n">
-        <v>10561.9</v>
+        <v>34115.9</v>
       </c>
       <c r="J46" t="n">
-        <v>14822.67</v>
+        <v>34115.9</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F47" t="n">
-        <v>261113.68</v>
+        <v>538037.9</v>
       </c>
       <c r="G47" t="n">
-        <v>20889.09</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>240224.58</v>
+        <v>355355.26</v>
       </c>
       <c r="I47" t="n">
-        <v>173097.83</v>
+        <v>538037.9</v>
       </c>
       <c r="J47" t="n">
-        <v>240224.58</v>
+        <v>538037.9</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2298,25 +2298,25 @@
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
         <v>2400</v>
       </c>
       <c r="F48" t="n">
-        <v>9601.73</v>
+        <v>28449.49</v>
       </c>
       <c r="G48" t="n">
-        <v>768.14</v>
+        <v>804.73</v>
       </c>
       <c r="H48" t="n">
-        <v>8833.59</v>
+        <v>17780.93</v>
       </c>
       <c r="I48" t="n">
-        <v>6001.08</v>
+        <v>27644.76</v>
       </c>
       <c r="J48" t="n">
-        <v>8833.59</v>
+        <v>27644.76</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="D49" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E49" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F49" t="n">
-        <v>36806.63</v>
+        <v>105105.08</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>36806.63</v>
+        <v>70070.05</v>
       </c>
       <c r="I49" t="n">
-        <v>25151.19</v>
+        <v>105105.08</v>
       </c>
       <c r="J49" t="n">
-        <v>36806.63</v>
+        <v>105105.08</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,37 +2364,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E50" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F50" t="n">
-        <v>102685.15</v>
+        <v>257889.4</v>
       </c>
       <c r="G50" t="n">
-        <v>5134.26</v>
+        <v>12157.85</v>
       </c>
       <c r="H50" t="n">
-        <v>97550.89999999999</v>
+        <v>170960.39</v>
       </c>
       <c r="I50" t="n">
-        <v>65345.1</v>
+        <v>245731.55</v>
       </c>
       <c r="J50" t="n">
-        <v>97550.89999999999</v>
+        <v>245731.55</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F51" t="n">
-        <v>284851.28</v>
+        <v>651309.04</v>
       </c>
       <c r="G51" t="n">
-        <v>14242.56</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>270608.72</v>
+        <v>430166.9</v>
       </c>
       <c r="I51" t="n">
-        <v>188834</v>
+        <v>651309.04</v>
       </c>
       <c r="J51" t="n">
-        <v>270608.72</v>
+        <v>651309.04</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,37 +2442,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E52" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F52" t="n">
-        <v>3467.29</v>
+        <v>466519.03</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>3467.29</v>
+        <v>296875.75</v>
       </c>
       <c r="I52" t="n">
-        <v>2347.09</v>
+        <v>466519.03</v>
       </c>
       <c r="J52" t="n">
-        <v>3467.29</v>
+        <v>466519.03</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,37 +2481,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="D53" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E53" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F53" t="n">
-        <v>308055.46</v>
+        <v>69543.21000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>9241.66</v>
+        <v>1967.11</v>
       </c>
       <c r="H53" t="n">
-        <v>298813.8</v>
+        <v>43464.51</v>
       </c>
       <c r="I53" t="n">
-        <v>196035.29</v>
+        <v>67576.10000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>298813.8</v>
+        <v>67576.10000000001</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2532,25 +2532,25 @@
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
         <v>15400</v>
       </c>
       <c r="F54" t="n">
-        <v>82148.12</v>
+        <v>162267.49</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>3059.95</v>
       </c>
       <c r="H54" t="n">
-        <v>82148.12</v>
+        <v>103261.13</v>
       </c>
       <c r="I54" t="n">
-        <v>52276.08</v>
+        <v>159207.54</v>
       </c>
       <c r="J54" t="n">
-        <v>82148.12</v>
+        <v>159207.54</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2571,25 +2571,25 @@
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E55" t="n">
         <v>8900</v>
       </c>
       <c r="F55" t="n">
-        <v>166163.25</v>
+        <v>269611.65</v>
       </c>
       <c r="G55" t="n">
-        <v>8308.16</v>
+        <v>7626.29</v>
       </c>
       <c r="H55" t="n">
-        <v>157855.09</v>
+        <v>178731.32</v>
       </c>
       <c r="I55" t="n">
-        <v>110153.16</v>
+        <v>261985.36</v>
       </c>
       <c r="J55" t="n">
-        <v>157855.09</v>
+        <v>261985.36</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2610,25 +2610,25 @@
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
         <v>2400</v>
       </c>
       <c r="F56" t="n">
-        <v>12802.3</v>
+        <v>9483.16</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>268.24</v>
       </c>
       <c r="H56" t="n">
-        <v>12802.3</v>
+        <v>5926.98</v>
       </c>
       <c r="I56" t="n">
-        <v>8001.44</v>
+        <v>9214.92</v>
       </c>
       <c r="J56" t="n">
-        <v>12802.3</v>
+        <v>9214.92</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E57" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F57" t="n">
-        <v>15602.81</v>
+        <v>538037.9</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>15219.05</v>
       </c>
       <c r="H57" t="n">
-        <v>15602.81</v>
+        <v>355355.26</v>
       </c>
       <c r="I57" t="n">
-        <v>10561.9</v>
+        <v>522818.85</v>
       </c>
       <c r="J57" t="n">
-        <v>15602.81</v>
+        <v>522818.85</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E58" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F58" t="n">
-        <v>11268.7</v>
+        <v>56898.99</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>11268.7</v>
+        <v>35561.87</v>
       </c>
       <c r="I58" t="n">
-        <v>7628.04</v>
+        <v>56898.99</v>
       </c>
       <c r="J58" t="n">
-        <v>11268.7</v>
+        <v>56898.99</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E59" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F59" t="n">
-        <v>41607.49</v>
+        <v>19690.74</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>928.29</v>
       </c>
       <c r="H59" t="n">
-        <v>41607.49</v>
+        <v>13329.12</v>
       </c>
       <c r="I59" t="n">
-        <v>26004.68</v>
+        <v>18762.45</v>
       </c>
       <c r="J59" t="n">
-        <v>41607.49</v>
+        <v>18762.45</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,37 +2754,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F60" t="n">
-        <v>30405.47</v>
+        <v>22127.38</v>
       </c>
       <c r="G60" t="n">
-        <v>2432.44</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>27973.04</v>
+        <v>14751.59</v>
       </c>
       <c r="I60" t="n">
-        <v>20777.07</v>
+        <v>22127.38</v>
       </c>
       <c r="J60" t="n">
-        <v>27973.04</v>
+        <v>22127.38</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,12 +2793,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -2808,22 +2808,22 @@
         <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F61" t="n">
-        <v>19203.46</v>
+        <v>5136.71</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>242.16</v>
       </c>
       <c r="H61" t="n">
-        <v>19203.46</v>
+        <v>3477.16</v>
       </c>
       <c r="I61" t="n">
-        <v>12002.16</v>
+        <v>4894.55</v>
       </c>
       <c r="J61" t="n">
-        <v>19203.46</v>
+        <v>4894.55</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,37 +2832,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E62" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F62" t="n">
-        <v>184833.28</v>
+        <v>79026.37</v>
       </c>
       <c r="G62" t="n">
-        <v>9241.66</v>
+        <v>1490.24</v>
       </c>
       <c r="H62" t="n">
-        <v>175591.61</v>
+        <v>49391.48</v>
       </c>
       <c r="I62" t="n">
-        <v>117621.18</v>
+        <v>77536.13</v>
       </c>
       <c r="J62" t="n">
-        <v>175591.61</v>
+        <v>77536.13</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,37 +2871,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F63" t="n">
-        <v>33606.05</v>
+        <v>12644.22</v>
       </c>
       <c r="G63" t="n">
-        <v>1680.3</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>31925.75</v>
+        <v>7902.64</v>
       </c>
       <c r="I63" t="n">
-        <v>22404.03</v>
+        <v>12644.22</v>
       </c>
       <c r="J63" t="n">
-        <v>31925.75</v>
+        <v>12644.22</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,37 +2910,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E64" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F64" t="n">
-        <v>32005.76</v>
+        <v>162267.49</v>
       </c>
       <c r="G64" t="n">
-        <v>1600.29</v>
+        <v>7649.88</v>
       </c>
       <c r="H64" t="n">
-        <v>30405.47</v>
+        <v>103261.13</v>
       </c>
       <c r="I64" t="n">
-        <v>20003.6</v>
+        <v>154617.61</v>
       </c>
       <c r="J64" t="n">
-        <v>30405.47</v>
+        <v>154617.61</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E65" t="n">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="F65" t="n">
-        <v>67212.10000000001</v>
+        <v>23707.91</v>
       </c>
       <c r="G65" t="n">
-        <v>2016.36</v>
+        <v>447.07</v>
       </c>
       <c r="H65" t="n">
-        <v>65195.74</v>
+        <v>16200.41</v>
       </c>
       <c r="I65" t="n">
-        <v>44808.07</v>
+        <v>23260.84</v>
       </c>
       <c r="J65" t="n">
-        <v>65195.74</v>
+        <v>23260.84</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,7 +2988,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3000,25 +3000,25 @@
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E66" t="n">
         <v>21500</v>
       </c>
       <c r="F66" t="n">
-        <v>573436.5699999999</v>
+        <v>707944.6</v>
       </c>
       <c r="G66" t="n">
-        <v>45874.93</v>
+        <v>33375.11</v>
       </c>
       <c r="H66" t="n">
-        <v>527561.64</v>
+        <v>467572.72</v>
       </c>
       <c r="I66" t="n">
-        <v>378734.85</v>
+        <v>674569.49</v>
       </c>
       <c r="J66" t="n">
-        <v>527561.64</v>
+        <v>674569.49</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E67" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F67" t="n">
-        <v>114687.31</v>
+        <v>140666.95</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>114687.31</v>
+        <v>93251.12</v>
       </c>
       <c r="I67" t="n">
-        <v>75746.97</v>
+        <v>140666.95</v>
       </c>
       <c r="J67" t="n">
-        <v>114687.31</v>
+        <v>140666.95</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F68" t="n">
-        <v>32072.44</v>
+        <v>55318.46</v>
       </c>
       <c r="G68" t="n">
-        <v>962.17</v>
+        <v>1564.75</v>
       </c>
       <c r="H68" t="n">
-        <v>31110.27</v>
+        <v>36878.97</v>
       </c>
       <c r="I68" t="n">
-        <v>21670.57</v>
+        <v>53753.71</v>
       </c>
       <c r="J68" t="n">
-        <v>31110.27</v>
+        <v>53753.71</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F69" t="n">
-        <v>35206.34</v>
+        <v>22127.38</v>
       </c>
       <c r="G69" t="n">
-        <v>1760.32</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>33446.02</v>
+        <v>14751.59</v>
       </c>
       <c r="I69" t="n">
-        <v>22003.96</v>
+        <v>22127.38</v>
       </c>
       <c r="J69" t="n">
-        <v>33446.02</v>
+        <v>22127.38</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3149,32 +3149,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="D70" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F70" t="n">
-        <v>67212.10000000001</v>
+        <v>223117.8</v>
       </c>
       <c r="G70" t="n">
-        <v>5376.97</v>
+        <v>6311.15</v>
       </c>
       <c r="H70" t="n">
-        <v>61835.13</v>
+        <v>141984.05</v>
       </c>
       <c r="I70" t="n">
-        <v>42007.56</v>
+        <v>216806.65</v>
       </c>
       <c r="J70" t="n">
-        <v>61835.13</v>
+        <v>216806.65</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E71" t="n">
-        <v>15400</v>
+        <v>1200</v>
       </c>
       <c r="F71" t="n">
-        <v>225907.34</v>
+        <v>26868.97</v>
       </c>
       <c r="G71" t="n">
-        <v>18072.59</v>
+        <v>760.02</v>
       </c>
       <c r="H71" t="n">
-        <v>207834.75</v>
+        <v>18360.46</v>
       </c>
       <c r="I71" t="n">
-        <v>143759.21</v>
+        <v>26108.95</v>
       </c>
       <c r="J71" t="n">
-        <v>207834.75</v>
+        <v>26108.95</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F72" t="n">
-        <v>25604.61</v>
+        <v>113271.14</v>
       </c>
       <c r="G72" t="n">
-        <v>768.14</v>
+        <v>3204.01</v>
       </c>
       <c r="H72" t="n">
-        <v>24836.47</v>
+        <v>74811.63</v>
       </c>
       <c r="I72" t="n">
-        <v>17496.48</v>
+        <v>110067.13</v>
       </c>
       <c r="J72" t="n">
-        <v>24836.47</v>
+        <v>110067.13</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,12 +3261,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -3276,22 +3276,22 @@
         <v>11</v>
       </c>
       <c r="E73" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F73" t="n">
-        <v>35206.34</v>
+        <v>311495.63</v>
       </c>
       <c r="G73" t="n">
-        <v>1056.19</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>34150.15</v>
+        <v>205731.99</v>
       </c>
       <c r="I73" t="n">
-        <v>22003.96</v>
+        <v>311495.63</v>
       </c>
       <c r="J73" t="n">
-        <v>34150.15</v>
+        <v>311495.63</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,37 +3300,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="D74" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E74" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F74" t="n">
-        <v>544764.74</v>
+        <v>56042.87</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>544764.74</v>
+        <v>37866.8</v>
       </c>
       <c r="I74" t="n">
-        <v>359798.11</v>
+        <v>56042.87</v>
       </c>
       <c r="J74" t="n">
-        <v>544764.74</v>
+        <v>56042.87</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E75" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F75" t="n">
-        <v>28805.19</v>
+        <v>17978.5</v>
       </c>
       <c r="G75" t="n">
-        <v>1440.26</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>27364.93</v>
+        <v>12170.06</v>
       </c>
       <c r="I75" t="n">
-        <v>18003.24</v>
+        <v>17978.5</v>
       </c>
       <c r="J75" t="n">
-        <v>27364.93</v>
+        <v>17978.5</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E76" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F76" t="n">
-        <v>106419.16</v>
+        <v>281333.89</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>106419.16</v>
+        <v>186502.24</v>
       </c>
       <c r="I76" t="n">
-        <v>70946.11</v>
+        <v>281333.89</v>
       </c>
       <c r="J76" t="n">
-        <v>106419.16</v>
+        <v>281333.89</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,7 +3417,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3429,25 +3429,25 @@
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E77" t="n">
         <v>8900</v>
       </c>
       <c r="F77" t="n">
-        <v>261113.68</v>
+        <v>211000.42</v>
       </c>
       <c r="G77" t="n">
-        <v>20889.09</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>240224.58</v>
+        <v>139876.68</v>
       </c>
       <c r="I77" t="n">
-        <v>173097.83</v>
+        <v>211000.42</v>
       </c>
       <c r="J77" t="n">
-        <v>240224.58</v>
+        <v>211000.42</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E78" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F78" t="n">
-        <v>659452.05</v>
+        <v>47415.82</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>659452.05</v>
+        <v>29634.89</v>
       </c>
       <c r="I78" t="n">
-        <v>435545.08</v>
+        <v>47415.82</v>
       </c>
       <c r="J78" t="n">
-        <v>659452.05</v>
+        <v>47415.82</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E79" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F79" t="n">
-        <v>472351.7</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>472351.7</v>
+        <v>41488.85</v>
       </c>
       <c r="I79" t="n">
-        <v>300587.45</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>472351.7</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3546,25 +3546,25 @@
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E80" t="n">
         <v>2400</v>
       </c>
       <c r="F80" t="n">
-        <v>70412.67999999999</v>
+        <v>41093.71</v>
       </c>
       <c r="G80" t="n">
-        <v>3520.63</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>66892.03999999999</v>
+        <v>25683.57</v>
       </c>
       <c r="I80" t="n">
-        <v>44007.92</v>
+        <v>41093.71</v>
       </c>
       <c r="J80" t="n">
-        <v>66892.03999999999</v>
+        <v>41093.71</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E81" t="n">
-        <v>15400</v>
+        <v>1200</v>
       </c>
       <c r="F81" t="n">
-        <v>164296.24</v>
+        <v>23707.91</v>
       </c>
       <c r="G81" t="n">
-        <v>4928.89</v>
+        <v>1117.68</v>
       </c>
       <c r="H81" t="n">
-        <v>159367.36</v>
+        <v>16200.41</v>
       </c>
       <c r="I81" t="n">
-        <v>104552.16</v>
+        <v>22590.23</v>
       </c>
       <c r="J81" t="n">
-        <v>159367.36</v>
+        <v>22590.23</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F82" t="n">
-        <v>272982.48</v>
+        <v>3161.05</v>
       </c>
       <c r="G82" t="n">
-        <v>13649.12</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>259333.35</v>
+        <v>1975.66</v>
       </c>
       <c r="I82" t="n">
-        <v>180965.91</v>
+        <v>3161.05</v>
       </c>
       <c r="J82" t="n">
-        <v>259333.35</v>
+        <v>3161.05</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E83" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F83" t="n">
-        <v>9601.73</v>
+        <v>507085.9</v>
       </c>
       <c r="G83" t="n">
-        <v>480.09</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>9121.639999999999</v>
+        <v>322691.03</v>
       </c>
       <c r="I83" t="n">
-        <v>6001.08</v>
+        <v>507085.9</v>
       </c>
       <c r="J83" t="n">
-        <v>9121.639999999999</v>
+        <v>507085.9</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3695,32 +3695,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E84" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F84" t="n">
-        <v>544764.74</v>
+        <v>99573.23</v>
       </c>
       <c r="G84" t="n">
-        <v>27238.24</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>517526.5</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>359798.11</v>
+        <v>99573.23</v>
       </c>
       <c r="J84" t="n">
-        <v>517526.5</v>
+        <v>99573.23</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E85" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F85" t="n">
-        <v>57610.37</v>
+        <v>5992.83</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>169.51</v>
       </c>
       <c r="H85" t="n">
-        <v>57610.37</v>
+        <v>4056.69</v>
       </c>
       <c r="I85" t="n">
-        <v>36006.48</v>
+        <v>5823.32</v>
       </c>
       <c r="J85" t="n">
-        <v>57610.37</v>
+        <v>5823.32</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E86" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F86" t="n">
-        <v>19936.92</v>
+        <v>446235.59</v>
       </c>
       <c r="G86" t="n">
-        <v>1594.95</v>
+        <v>12622.31</v>
       </c>
       <c r="H86" t="n">
-        <v>18341.97</v>
+        <v>283968.11</v>
       </c>
       <c r="I86" t="n">
-        <v>13495.76</v>
+        <v>433613.28</v>
       </c>
       <c r="J86" t="n">
-        <v>18341.97</v>
+        <v>433613.28</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,37 +3807,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E87" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F87" t="n">
-        <v>22404.03</v>
+        <v>17122.38</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>484.33</v>
       </c>
       <c r="H87" t="n">
-        <v>22404.03</v>
+        <v>11590.53</v>
       </c>
       <c r="I87" t="n">
-        <v>14936.02</v>
+        <v>16638.05</v>
       </c>
       <c r="J87" t="n">
-        <v>22404.03</v>
+        <v>16638.05</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E88" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F88" t="n">
-        <v>5200.94</v>
+        <v>60060.04</v>
       </c>
       <c r="G88" t="n">
-        <v>624.11</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>4576.82</v>
+        <v>37537.53</v>
       </c>
       <c r="I88" t="n">
-        <v>3520.63</v>
+        <v>60060.04</v>
       </c>
       <c r="J88" t="n">
-        <v>4576.82</v>
+        <v>60060.04</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,37 +3885,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F89" t="n">
-        <v>46875.11</v>
+        <v>12841.79</v>
       </c>
       <c r="G89" t="n">
-        <v>5625.01</v>
+        <v>605.41</v>
       </c>
       <c r="H89" t="n">
-        <v>41250.09</v>
+        <v>8692.9</v>
       </c>
       <c r="I89" t="n">
-        <v>31672.37</v>
+        <v>12236.38</v>
       </c>
       <c r="J89" t="n">
-        <v>41250.09</v>
+        <v>12236.38</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E90" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F90" t="n">
-        <v>80014.41</v>
+        <v>405668.72</v>
       </c>
       <c r="G90" t="n">
-        <v>2400.43</v>
+        <v>19124.71</v>
       </c>
       <c r="H90" t="n">
-        <v>77613.97</v>
+        <v>258152.82</v>
       </c>
       <c r="I90" t="n">
-        <v>50009</v>
+        <v>386544.01</v>
       </c>
       <c r="J90" t="n">
-        <v>77613.97</v>
+        <v>386544.01</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E91" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F91" t="n">
-        <v>12802.3</v>
+        <v>128944.7</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>12802.3</v>
+        <v>85480.19</v>
       </c>
       <c r="I91" t="n">
-        <v>8001.44</v>
+        <v>128944.7</v>
       </c>
       <c r="J91" t="n">
-        <v>12802.3</v>
+        <v>128944.7</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,7 +4002,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4014,25 +4014,25 @@
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
         <v>15400</v>
       </c>
       <c r="F92" t="n">
-        <v>164296.24</v>
+        <v>81133.74000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>13143.7</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>151152.55</v>
+        <v>51630.56</v>
       </c>
       <c r="I92" t="n">
-        <v>104552.16</v>
+        <v>81133.74000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>151152.55</v>
+        <v>81133.74000000001</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E93" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F93" t="n">
-        <v>24004.32</v>
+        <v>199278.17</v>
       </c>
       <c r="G93" t="n">
-        <v>720.13</v>
+        <v>5636.82</v>
       </c>
       <c r="H93" t="n">
-        <v>23284.19</v>
+        <v>132105.76</v>
       </c>
       <c r="I93" t="n">
-        <v>16402.95</v>
+        <v>193641.35</v>
       </c>
       <c r="J93" t="n">
-        <v>23284.19</v>
+        <v>193641.35</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4085,32 +4085,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E94" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F94" t="n">
-        <v>716795.71</v>
+        <v>222722.67</v>
       </c>
       <c r="G94" t="n">
-        <v>86015.49000000001</v>
+        <v>6299.98</v>
       </c>
       <c r="H94" t="n">
-        <v>630780.23</v>
+        <v>147647.61</v>
       </c>
       <c r="I94" t="n">
-        <v>473418.56</v>
+        <v>216422.69</v>
       </c>
       <c r="J94" t="n">
-        <v>630780.23</v>
+        <v>216422.69</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4131,25 +4131,25 @@
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E95" t="n">
         <v>8900</v>
       </c>
       <c r="F95" t="n">
-        <v>142425.64</v>
+        <v>187555.93</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>8842.07</v>
       </c>
       <c r="H95" t="n">
-        <v>142425.64</v>
+        <v>124334.83</v>
       </c>
       <c r="I95" t="n">
-        <v>94417</v>
+        <v>178713.86</v>
       </c>
       <c r="J95" t="n">
-        <v>142425.64</v>
+        <v>178713.86</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E96" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F96" t="n">
-        <v>56010.08</v>
+        <v>211000.42</v>
       </c>
       <c r="G96" t="n">
-        <v>2800.5</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>53209.58</v>
+        <v>139876.68</v>
       </c>
       <c r="I96" t="n">
-        <v>37340.06</v>
+        <v>211000.42</v>
       </c>
       <c r="J96" t="n">
-        <v>53209.58</v>
+        <v>211000.42</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E97" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F97" t="n">
-        <v>22404.03</v>
+        <v>101417.18</v>
       </c>
       <c r="G97" t="n">
-        <v>2688.48</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>19715.55</v>
+        <v>64538.21</v>
       </c>
       <c r="I97" t="n">
-        <v>14936.02</v>
+        <v>101417.18</v>
       </c>
       <c r="J97" t="n">
-        <v>19715.55</v>
+        <v>101417.18</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,37 +4236,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E98" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F98" t="n">
-        <v>8668.23</v>
+        <v>566355.6800000001</v>
       </c>
       <c r="G98" t="n">
-        <v>260.05</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>8408.18</v>
+        <v>374058.17</v>
       </c>
       <c r="I98" t="n">
-        <v>5867.72</v>
+        <v>566355.6800000001</v>
       </c>
       <c r="J98" t="n">
-        <v>8408.18</v>
+        <v>566355.6800000001</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F99" t="n">
-        <v>27204.9</v>
+        <v>856.12</v>
       </c>
       <c r="G99" t="n">
-        <v>1360.24</v>
+        <v>24.22</v>
       </c>
       <c r="H99" t="n">
-        <v>25844.65</v>
+        <v>579.53</v>
       </c>
       <c r="I99" t="n">
-        <v>18590.01</v>
+        <v>831.9</v>
       </c>
       <c r="J99" t="n">
-        <v>25844.65</v>
+        <v>831.9</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E100" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F100" t="n">
-        <v>114687.31</v>
+        <v>20546.86</v>
       </c>
       <c r="G100" t="n">
-        <v>5734.37</v>
+        <v>968.65</v>
       </c>
       <c r="H100" t="n">
-        <v>108952.95</v>
+        <v>14040.35</v>
       </c>
       <c r="I100" t="n">
-        <v>75746.97</v>
+        <v>19578.21</v>
       </c>
       <c r="J100" t="n">
-        <v>108952.95</v>
+        <v>19578.21</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,7 +4353,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4365,25 +4365,25 @@
         <v>45858</v>
       </c>
       <c r="D101" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E101" t="n">
         <v>21500</v>
       </c>
       <c r="F101" t="n">
-        <v>315390.11</v>
+        <v>396448.98</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>11214.04</v>
       </c>
       <c r="H101" t="n">
-        <v>315390.11</v>
+        <v>261840.72</v>
       </c>
       <c r="I101" t="n">
-        <v>208304.17</v>
+        <v>385234.94</v>
       </c>
       <c r="J101" t="n">
-        <v>315390.11</v>
+        <v>385234.94</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,37 +4392,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E102" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F102" t="n">
-        <v>56743.55</v>
+        <v>453084.55</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>56743.55</v>
+        <v>299246.54</v>
       </c>
       <c r="I102" t="n">
-        <v>38340.24</v>
+        <v>453084.55</v>
       </c>
       <c r="J102" t="n">
-        <v>56743.55</v>
+        <v>453084.55</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E103" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F103" t="n">
-        <v>18203.28</v>
+        <v>60916.16</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>18203.28</v>
+        <v>41159.57</v>
       </c>
       <c r="I103" t="n">
-        <v>12322.22</v>
+        <v>60916.16</v>
       </c>
       <c r="J103" t="n">
-        <v>18203.28</v>
+        <v>60916.16</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E104" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F104" t="n">
-        <v>284851.28</v>
+        <v>21929.82</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>284851.28</v>
+        <v>14817.45</v>
       </c>
       <c r="I104" t="n">
-        <v>188834</v>
+        <v>21929.82</v>
       </c>
       <c r="J104" t="n">
-        <v>284851.28</v>
+        <v>21929.82</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4514,32 +4514,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E105" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F105" t="n">
-        <v>213638.46</v>
+        <v>121700.62</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>3442.45</v>
       </c>
       <c r="H105" t="n">
-        <v>213638.46</v>
+        <v>77445.85000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>141625.5</v>
+        <v>118258.17</v>
       </c>
       <c r="J105" t="n">
-        <v>213638.46</v>
+        <v>118258.17</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E106" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F106" t="n">
-        <v>48008.64</v>
+        <v>509720.11</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>24030.08</v>
       </c>
       <c r="H106" t="n">
-        <v>48008.64</v>
+        <v>336652.35</v>
       </c>
       <c r="I106" t="n">
-        <v>30005.4</v>
+        <v>485690.03</v>
       </c>
       <c r="J106" t="n">
-        <v>48008.64</v>
+        <v>485690.03</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,37 +4587,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E107" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F107" t="n">
-        <v>67212.10000000001</v>
+        <v>49786.62</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>2347.12</v>
       </c>
       <c r="H107" t="n">
-        <v>67212.10000000001</v>
+        <v>33191.08</v>
       </c>
       <c r="I107" t="n">
-        <v>42007.56</v>
+        <v>47439.5</v>
       </c>
       <c r="J107" t="n">
-        <v>67212.10000000001</v>
+        <v>47439.5</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E108" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F108" t="n">
-        <v>41607.49</v>
+        <v>15410.14</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>41607.49</v>
+        <v>10431.48</v>
       </c>
       <c r="I108" t="n">
-        <v>26004.68</v>
+        <v>15410.14</v>
       </c>
       <c r="J108" t="n">
-        <v>41607.49</v>
+        <v>15410.14</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E109" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F109" t="n">
-        <v>24004.32</v>
+        <v>509720.11</v>
       </c>
       <c r="G109" t="n">
-        <v>1920.35</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>22083.98</v>
+        <v>336652.35</v>
       </c>
       <c r="I109" t="n">
-        <v>16402.95</v>
+        <v>509720.11</v>
       </c>
       <c r="J109" t="n">
-        <v>22083.98</v>
+        <v>509720.11</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4709,32 +4709,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E110" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F110" t="n">
-        <v>3200.58</v>
+        <v>132764.31</v>
       </c>
       <c r="G110" t="n">
-        <v>384.07</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>2816.51</v>
+        <v>88509.53999999999</v>
       </c>
       <c r="I110" t="n">
-        <v>2000.36</v>
+        <v>132764.31</v>
       </c>
       <c r="J110" t="n">
-        <v>2816.51</v>
+        <v>132764.31</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,37 +4743,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E111" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F111" t="n">
-        <v>14402.59</v>
+        <v>36549.7</v>
       </c>
       <c r="G111" t="n">
-        <v>1728.31</v>
+        <v>689.23</v>
       </c>
       <c r="H111" t="n">
-        <v>12674.28</v>
+        <v>24695.74</v>
       </c>
       <c r="I111" t="n">
-        <v>9841.77</v>
+        <v>35860.47</v>
       </c>
       <c r="J111" t="n">
-        <v>12674.28</v>
+        <v>35860.47</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4794,25 +4794,25 @@
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E112" t="n">
         <v>4200</v>
       </c>
       <c r="F112" t="n">
-        <v>106419.16</v>
+        <v>82977.69</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>106419.16</v>
+        <v>55318.46</v>
       </c>
       <c r="I112" t="n">
-        <v>70946.11</v>
+        <v>82977.69</v>
       </c>
       <c r="J112" t="n">
-        <v>106419.16</v>
+        <v>82977.69</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4826,32 +4826,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E113" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F113" t="n">
-        <v>142425.64</v>
+        <v>11063.69</v>
       </c>
       <c r="G113" t="n">
-        <v>4272.77</v>
+        <v>521.58</v>
       </c>
       <c r="H113" t="n">
-        <v>138152.87</v>
+        <v>7560.19</v>
       </c>
       <c r="I113" t="n">
-        <v>94417</v>
+        <v>10542.11</v>
       </c>
       <c r="J113" t="n">
-        <v>138152.87</v>
+        <v>10542.11</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E114" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F114" t="n">
-        <v>114687.31</v>
+        <v>19690.74</v>
       </c>
       <c r="G114" t="n">
-        <v>3440.62</v>
+        <v>928.29</v>
       </c>
       <c r="H114" t="n">
-        <v>111246.69</v>
+        <v>13329.12</v>
       </c>
       <c r="I114" t="n">
-        <v>75746.97</v>
+        <v>18762.45</v>
       </c>
       <c r="J114" t="n">
-        <v>111246.69</v>
+        <v>18762.45</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4904,32 +4904,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E115" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F115" t="n">
-        <v>487421.08</v>
+        <v>18966.33</v>
       </c>
       <c r="G115" t="n">
-        <v>58490.53</v>
+        <v>894.14</v>
       </c>
       <c r="H115" t="n">
-        <v>428930.55</v>
+        <v>11853.96</v>
       </c>
       <c r="I115" t="n">
-        <v>321924.62</v>
+        <v>18072.19</v>
       </c>
       <c r="J115" t="n">
-        <v>428930.55</v>
+        <v>18072.19</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E116" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F116" t="n">
-        <v>64011.52</v>
+        <v>11063.69</v>
       </c>
       <c r="G116" t="n">
-        <v>3200.58</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>60810.95</v>
+        <v>7560.19</v>
       </c>
       <c r="I116" t="n">
-        <v>40007.2</v>
+        <v>11063.69</v>
       </c>
       <c r="J116" t="n">
-        <v>60810.95</v>
+        <v>11063.69</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4982,32 +4982,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E117" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F117" t="n">
-        <v>67212.10000000001</v>
+        <v>15410.14</v>
       </c>
       <c r="G117" t="n">
-        <v>2016.36</v>
+        <v>290.6</v>
       </c>
       <c r="H117" t="n">
-        <v>65195.74</v>
+        <v>10431.48</v>
       </c>
       <c r="I117" t="n">
-        <v>44808.07</v>
+        <v>15119.54</v>
       </c>
       <c r="J117" t="n">
-        <v>65195.74</v>
+        <v>15119.54</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E118" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F118" t="n">
-        <v>573436.5699999999</v>
+        <v>128944.7</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>2431.57</v>
       </c>
       <c r="H118" t="n">
-        <v>573436.5699999999</v>
+        <v>85480.19</v>
       </c>
       <c r="I118" t="n">
-        <v>378734.85</v>
+        <v>126513.13</v>
       </c>
       <c r="J118" t="n">
-        <v>573436.5699999999</v>
+        <v>126513.13</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5067,25 +5067,25 @@
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E119" t="n">
         <v>15400</v>
       </c>
       <c r="F119" t="n">
-        <v>410740.61</v>
+        <v>344818.41</v>
       </c>
       <c r="G119" t="n">
-        <v>32859.25</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>377881.36</v>
+        <v>219429.9</v>
       </c>
       <c r="I119" t="n">
-        <v>261380.39</v>
+        <v>344818.41</v>
       </c>
       <c r="J119" t="n">
-        <v>377881.36</v>
+        <v>344818.41</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F120" t="n">
-        <v>130556.84</v>
+        <v>6322.11</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>119.22</v>
       </c>
       <c r="H120" t="n">
-        <v>130556.84</v>
+        <v>3951.32</v>
       </c>
       <c r="I120" t="n">
-        <v>86548.91</v>
+        <v>6202.89</v>
       </c>
       <c r="J120" t="n">
-        <v>130556.84</v>
+        <v>6202.89</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E121" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F121" t="n">
-        <v>82148.12</v>
+        <v>269611.65</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>82148.12</v>
+        <v>178731.32</v>
       </c>
       <c r="I121" t="n">
-        <v>52276.08</v>
+        <v>269611.65</v>
       </c>
       <c r="J121" t="n">
-        <v>82148.12</v>
+        <v>269611.65</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,7 +5172,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5184,25 +5184,25 @@
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E122" t="n">
         <v>8900</v>
       </c>
       <c r="F122" t="n">
-        <v>201769.66</v>
+        <v>269611.65</v>
       </c>
       <c r="G122" t="n">
-        <v>10088.48</v>
+        <v>5084.19</v>
       </c>
       <c r="H122" t="n">
-        <v>191681.18</v>
+        <v>178731.32</v>
       </c>
       <c r="I122" t="n">
-        <v>133757.41</v>
+        <v>264527.46</v>
       </c>
       <c r="J122" t="n">
-        <v>191681.18</v>
+        <v>264527.46</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5211,37 +5211,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E123" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F123" t="n">
-        <v>225507.26</v>
+        <v>39513.19</v>
       </c>
       <c r="G123" t="n">
-        <v>11275.36</v>
+        <v>1117.68</v>
       </c>
       <c r="H123" t="n">
-        <v>214231.9</v>
+        <v>27000.68</v>
       </c>
       <c r="I123" t="n">
-        <v>149493.58</v>
+        <v>38395.51</v>
       </c>
       <c r="J123" t="n">
-        <v>214231.9</v>
+        <v>38395.51</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5262,25 +5262,25 @@
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E124" t="n">
         <v>8900</v>
       </c>
       <c r="F124" t="n">
-        <v>189900.85</v>
+        <v>222722.67</v>
       </c>
       <c r="G124" t="n">
-        <v>22788.1</v>
+        <v>4199.99</v>
       </c>
       <c r="H124" t="n">
-        <v>167112.75</v>
+        <v>147647.61</v>
       </c>
       <c r="I124" t="n">
-        <v>125889.33</v>
+        <v>218522.68</v>
       </c>
       <c r="J124" t="n">
-        <v>167112.75</v>
+        <v>218522.68</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,37 +5289,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E125" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F125" t="n">
-        <v>213638.46</v>
+        <v>41093.71</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>1162.39</v>
       </c>
       <c r="H125" t="n">
-        <v>213638.46</v>
+        <v>25683.57</v>
       </c>
       <c r="I125" t="n">
-        <v>141625.5</v>
+        <v>39931.32</v>
       </c>
       <c r="J125" t="n">
-        <v>213638.46</v>
+        <v>39931.32</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E126" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F126" t="n">
-        <v>102685.15</v>
+        <v>71914</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>3390.29</v>
       </c>
       <c r="H126" t="n">
-        <v>102685.15</v>
+        <v>47942.67</v>
       </c>
       <c r="I126" t="n">
-        <v>65345.1</v>
+        <v>68523.71000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>102685.15</v>
+        <v>68523.71000000001</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E127" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F127" t="n">
-        <v>573436.5699999999</v>
+        <v>466519.03</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>8797.370000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>573436.5699999999</v>
+        <v>296875.75</v>
       </c>
       <c r="I127" t="n">
-        <v>378734.85</v>
+        <v>457721.66</v>
       </c>
       <c r="J127" t="n">
-        <v>573436.5699999999</v>
+        <v>457721.66</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E128" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F128" t="n">
-        <v>866.8200000000001</v>
+        <v>311495.63</v>
       </c>
       <c r="G128" t="n">
-        <v>43.34</v>
+        <v>14685.05</v>
       </c>
       <c r="H128" t="n">
-        <v>823.48</v>
+        <v>205731.99</v>
       </c>
       <c r="I128" t="n">
-        <v>586.77</v>
+        <v>296810.58</v>
       </c>
       <c r="J128" t="n">
-        <v>823.48</v>
+        <v>296810.58</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E129" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F129" t="n">
-        <v>20803.75</v>
+        <v>132764.31</v>
       </c>
       <c r="G129" t="n">
-        <v>1664.3</v>
+        <v>3755.4</v>
       </c>
       <c r="H129" t="n">
-        <v>19139.45</v>
+        <v>88509.53999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>14215.89</v>
+        <v>129008.91</v>
       </c>
       <c r="J129" t="n">
-        <v>19139.45</v>
+        <v>129008.91</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E130" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F130" t="n">
-        <v>401405.6</v>
+        <v>2568.36</v>
       </c>
       <c r="G130" t="n">
-        <v>48168.67</v>
+        <v>121.08</v>
       </c>
       <c r="H130" t="n">
-        <v>353236.93</v>
+        <v>1738.58</v>
       </c>
       <c r="I130" t="n">
-        <v>265114.4</v>
+        <v>2447.28</v>
       </c>
       <c r="J130" t="n">
-        <v>353236.93</v>
+        <v>2447.28</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,37 +5523,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E131" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F131" t="n">
-        <v>73613.25</v>
+        <v>22127.38</v>
       </c>
       <c r="G131" t="n">
-        <v>3680.66</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>69932.59</v>
+        <v>15120.38</v>
       </c>
       <c r="I131" t="n">
-        <v>46008.28</v>
+        <v>22127.38</v>
       </c>
       <c r="J131" t="n">
-        <v>69932.59</v>
+        <v>22127.38</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5567,32 +5567,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E132" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F132" t="n">
-        <v>35606.41</v>
+        <v>223117.8</v>
       </c>
       <c r="G132" t="n">
-        <v>2848.51</v>
+        <v>4207.44</v>
       </c>
       <c r="H132" t="n">
-        <v>32757.9</v>
+        <v>141984.05</v>
       </c>
       <c r="I132" t="n">
-        <v>23604.25</v>
+        <v>218910.36</v>
       </c>
       <c r="J132" t="n">
-        <v>32757.9</v>
+        <v>218910.36</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E133" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F133" t="n">
-        <v>16002.88</v>
+        <v>222722.67</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>6299.98</v>
       </c>
       <c r="H133" t="n">
-        <v>16002.88</v>
+        <v>147647.61</v>
       </c>
       <c r="I133" t="n">
-        <v>10935.3</v>
+        <v>216422.69</v>
       </c>
       <c r="J133" t="n">
-        <v>16002.88</v>
+        <v>216422.69</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E134" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F134" t="n">
-        <v>28805.19</v>
+        <v>18834.62</v>
       </c>
       <c r="G134" t="n">
-        <v>864.16</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>27941.03</v>
+        <v>12749.59</v>
       </c>
       <c r="I134" t="n">
-        <v>19683.54</v>
+        <v>18834.62</v>
       </c>
       <c r="J134" t="n">
-        <v>27941.03</v>
+        <v>18834.62</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E135" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F135" t="n">
-        <v>544764.74</v>
+        <v>116168.77</v>
       </c>
       <c r="G135" t="n">
-        <v>65371.77</v>
+        <v>3285.97</v>
       </c>
       <c r="H135" t="n">
-        <v>479392.97</v>
+        <v>77445.85000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>359798.11</v>
+        <v>112882.8</v>
       </c>
       <c r="J135" t="n">
-        <v>479392.97</v>
+        <v>112882.8</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,37 +5718,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="D136" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E136" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F136" t="n">
-        <v>516092.91</v>
+        <v>33191.08</v>
       </c>
       <c r="G136" t="n">
-        <v>41287.43</v>
+        <v>938.85</v>
       </c>
       <c r="H136" t="n">
-        <v>474805.48</v>
+        <v>22127.38</v>
       </c>
       <c r="I136" t="n">
-        <v>340861.37</v>
+        <v>32252.23</v>
       </c>
       <c r="J136" t="n">
-        <v>474805.48</v>
+        <v>32252.23</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5757,37 +5757,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E137" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F137" t="n">
-        <v>50409.08</v>
+        <v>34113.05</v>
       </c>
       <c r="G137" t="n">
-        <v>4032.73</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>46376.35</v>
+        <v>23049.36</v>
       </c>
       <c r="I137" t="n">
-        <v>33606.05</v>
+        <v>34113.05</v>
       </c>
       <c r="J137" t="n">
-        <v>46376.35</v>
+        <v>34113.05</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5796,37 +5796,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E138" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F138" t="n">
-        <v>15602.81</v>
+        <v>246167.16</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>4642.09</v>
       </c>
       <c r="H138" t="n">
-        <v>15602.81</v>
+        <v>163189.46</v>
       </c>
       <c r="I138" t="n">
-        <v>10561.9</v>
+        <v>241525.07</v>
       </c>
       <c r="J138" t="n">
-        <v>15602.81</v>
+        <v>241525.07</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5835,37 +5835,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E139" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F139" t="n">
-        <v>516092.91</v>
+        <v>60850.31</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>1147.48</v>
       </c>
       <c r="H139" t="n">
-        <v>516092.91</v>
+        <v>38722.92</v>
       </c>
       <c r="I139" t="n">
-        <v>340861.37</v>
+        <v>59702.83</v>
       </c>
       <c r="J139" t="n">
-        <v>516092.91</v>
+        <v>59702.83</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5886,25 +5886,25 @@
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E140" t="n">
         <v>4200</v>
       </c>
       <c r="F140" t="n">
-        <v>134424.2</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="G140" t="n">
-        <v>16130.9</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>118293.3</v>
+        <v>44254.77</v>
       </c>
       <c r="I140" t="n">
-        <v>89616.13</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="J140" t="n">
-        <v>118293.3</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5913,37 +5913,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E141" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F141" t="n">
-        <v>16002.88</v>
+        <v>66382.14999999999</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1251.8</v>
       </c>
       <c r="H141" t="n">
-        <v>16002.88</v>
+        <v>41488.85</v>
       </c>
       <c r="I141" t="n">
-        <v>10935.3</v>
+        <v>65130.35</v>
       </c>
       <c r="J141" t="n">
-        <v>16002.88</v>
+        <v>65130.35</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5952,37 +5952,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E142" t="n">
-        <v>15400</v>
+        <v>1200</v>
       </c>
       <c r="F142" t="n">
-        <v>246444.37</v>
+        <v>22127.38</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>246444.37</v>
+        <v>15120.38</v>
       </c>
       <c r="I142" t="n">
-        <v>156828.23</v>
+        <v>22127.38</v>
       </c>
       <c r="J142" t="n">
-        <v>246444.37</v>
+        <v>22127.38</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5991,7 +5991,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -6003,25 +6003,25 @@
         <v>45943</v>
       </c>
       <c r="D143" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
         <v>4200</v>
       </c>
       <c r="F143" t="n">
-        <v>140025.21</v>
+        <v>5531.85</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>140025.21</v>
+        <v>3687.9</v>
       </c>
       <c r="I143" t="n">
-        <v>93350.14</v>
+        <v>5531.85</v>
       </c>
       <c r="J143" t="n">
-        <v>140025.21</v>
+        <v>5531.85</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6030,37 +6030,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E144" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F144" t="n">
-        <v>19936.92</v>
+        <v>27659.23</v>
       </c>
       <c r="G144" t="n">
-        <v>1594.95</v>
+        <v>1303.96</v>
       </c>
       <c r="H144" t="n">
-        <v>18341.97</v>
+        <v>18439.49</v>
       </c>
       <c r="I144" t="n">
-        <v>13495.76</v>
+        <v>26355.27</v>
       </c>
       <c r="J144" t="n">
-        <v>18341.97</v>
+        <v>26355.27</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6069,37 +6069,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F145" t="n">
-        <v>19203.46</v>
+        <v>28317.78</v>
       </c>
       <c r="G145" t="n">
-        <v>1536.28</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>17667.18</v>
+        <v>18702.91</v>
       </c>
       <c r="I145" t="n">
-        <v>12002.16</v>
+        <v>28317.78</v>
       </c>
       <c r="J145" t="n">
-        <v>17667.18</v>
+        <v>28317.78</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6108,37 +6108,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E146" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F146" t="n">
-        <v>11202.02</v>
+        <v>3424.48</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>96.87</v>
       </c>
       <c r="H146" t="n">
-        <v>11202.02</v>
+        <v>2318.11</v>
       </c>
       <c r="I146" t="n">
-        <v>7654.71</v>
+        <v>3327.61</v>
       </c>
       <c r="J146" t="n">
-        <v>11202.02</v>
+        <v>3327.61</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6147,118 +6147,118 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E147" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F147" t="n">
-        <v>15602.81</v>
+        <v>187555.93</v>
       </c>
       <c r="G147" t="n">
-        <v>468.08</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>15134.72</v>
+        <v>124334.83</v>
       </c>
       <c r="I147" t="n">
-        <v>10561.9</v>
+        <v>187555.93</v>
       </c>
       <c r="J147" t="n">
-        <v>7567.36</v>
+        <v>56266.78</v>
       </c>
       <c r="K147" t="n">
-        <v>7567.36</v>
+        <v>131289.15</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E148" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F148" t="n">
-        <v>130556.84</v>
+        <v>9483.16</v>
       </c>
       <c r="G148" t="n">
-        <v>15666.82</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>114890.02</v>
+        <v>5926.98</v>
       </c>
       <c r="I148" t="n">
-        <v>86548.91</v>
+        <v>9483.16</v>
       </c>
       <c r="J148" t="n">
-        <v>34467.01</v>
+        <v>4741.58</v>
       </c>
       <c r="K148" t="n">
-        <v>80423.00999999999</v>
+        <v>4741.58</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E149" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F149" t="n">
-        <v>349129.52</v>
+        <v>10273.43</v>
       </c>
       <c r="G149" t="n">
-        <v>41895.54</v>
+        <v>193.73</v>
       </c>
       <c r="H149" t="n">
-        <v>307233.98</v>
+        <v>6954.32</v>
       </c>
       <c r="I149" t="n">
-        <v>222173.33</v>
+        <v>10079.7</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>5039.85</v>
       </c>
       <c r="K149" t="n">
-        <v>307233.98</v>
+        <v>5039.85</v>
       </c>
     </row>
     <row r="150">
@@ -6276,34 +6276,34 @@
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E150" t="n">
         <v>2400</v>
       </c>
       <c r="F150" t="n">
-        <v>6401.15</v>
+        <v>79026.37</v>
       </c>
       <c r="G150" t="n">
-        <v>192.03</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>6209.12</v>
+        <v>49391.48</v>
       </c>
       <c r="I150" t="n">
-        <v>4000.72</v>
+        <v>79026.37</v>
       </c>
       <c r="J150" t="n">
-        <v>3104.56</v>
+        <v>39513.18</v>
       </c>
       <c r="K150" t="n">
-        <v>3104.56</v>
+        <v>39513.19</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6315,67 +6315,67 @@
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E151" t="n">
         <v>8900</v>
       </c>
       <c r="F151" t="n">
-        <v>94950.42999999999</v>
+        <v>35166.74</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1657.89</v>
       </c>
       <c r="H151" t="n">
-        <v>94950.42999999999</v>
+        <v>23312.78</v>
       </c>
       <c r="I151" t="n">
-        <v>62944.67</v>
+        <v>33508.85</v>
       </c>
       <c r="J151" t="n">
-        <v>47475.21</v>
+        <v>10052.65</v>
       </c>
       <c r="K151" t="n">
-        <v>47475.21</v>
+        <v>23456.2</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E152" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F152" t="n">
-        <v>40007.2</v>
+        <v>48732.93</v>
       </c>
       <c r="G152" t="n">
-        <v>4800.86</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>35206.34</v>
+        <v>32927.66</v>
       </c>
       <c r="I152" t="n">
-        <v>27338.26</v>
+        <v>48732.93</v>
       </c>
       <c r="J152" t="n">
-        <v>10561.9</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>24644.44</v>
+        <v>48732.93</v>
       </c>
     </row>
     <row r="153">
@@ -6386,35 +6386,35 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E153" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F153" t="n">
-        <v>225507.26</v>
+        <v>20546.86</v>
       </c>
       <c r="G153" t="n">
-        <v>27060.87</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>198446.39</v>
+        <v>13908.64</v>
       </c>
       <c r="I153" t="n">
-        <v>149493.58</v>
+        <v>20546.86</v>
       </c>
       <c r="J153" t="n">
-        <v>59533.92</v>
+        <v>6164.06</v>
       </c>
       <c r="K153" t="n">
-        <v>138912.48</v>
+        <v>14382.8</v>
       </c>
     </row>
     <row r="154">
@@ -6425,35 +6425,35 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E154" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F154" t="n">
-        <v>41607.49</v>
+        <v>164111.44</v>
       </c>
       <c r="G154" t="n">
-        <v>2080.37</v>
+        <v>7736.82</v>
       </c>
       <c r="H154" t="n">
-        <v>39527.12</v>
+        <v>108792.98</v>
       </c>
       <c r="I154" t="n">
-        <v>26004.68</v>
+        <v>156374.62</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>39527.12</v>
+        <v>156374.62</v>
       </c>
     </row>
     <row r="155">
@@ -6464,74 +6464,74 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E155" t="n">
-        <v>4200</v>
+        <v>21500</v>
       </c>
       <c r="F155" t="n">
-        <v>72813.11</v>
+        <v>198224.49</v>
       </c>
       <c r="G155" t="n">
-        <v>5825.05</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>66988.06</v>
+        <v>130920.36</v>
       </c>
       <c r="I155" t="n">
-        <v>48542.07</v>
+        <v>198224.49</v>
       </c>
       <c r="J155" t="n">
-        <v>33494.03</v>
+        <v>99112.24000000001</v>
       </c>
       <c r="K155" t="n">
-        <v>33494.03</v>
+        <v>99112.25</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E156" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F156" t="n">
-        <v>13002.34</v>
+        <v>27659.23</v>
       </c>
       <c r="G156" t="n">
-        <v>650.12</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>12352.22</v>
+        <v>18439.49</v>
       </c>
       <c r="I156" t="n">
-        <v>8801.58</v>
+        <v>27659.23</v>
       </c>
       <c r="J156" t="n">
-        <v>3705.67</v>
+        <v>8297.77</v>
       </c>
       <c r="K156" t="n">
-        <v>8646.559999999999</v>
+        <v>19361.46</v>
       </c>
     </row>
     <row r="157">
@@ -6542,80 +6542,80 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E157" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F157" t="n">
-        <v>61677.77</v>
+        <v>37932.66</v>
       </c>
       <c r="G157" t="n">
-        <v>7401.33</v>
+        <v>1072.97</v>
       </c>
       <c r="H157" t="n">
-        <v>54276.44</v>
+        <v>23707.91</v>
       </c>
       <c r="I157" t="n">
-        <v>41674.17</v>
+        <v>36859.69</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>18429.85</v>
       </c>
       <c r="K157" t="n">
-        <v>54276.44</v>
+        <v>18429.84</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E158" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F158" t="n">
-        <v>602108.4</v>
+        <v>93777.96000000001</v>
       </c>
       <c r="G158" t="n">
-        <v>72253.00999999999</v>
+        <v>1768.41</v>
       </c>
       <c r="H158" t="n">
-        <v>529855.39</v>
+        <v>62167.41</v>
       </c>
       <c r="I158" t="n">
-        <v>397671.59</v>
+        <v>92009.55</v>
       </c>
       <c r="J158" t="n">
-        <v>264927.7</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>264927.7</v>
+        <v>92009.55</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6627,67 +6627,67 @@
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E159" t="n">
         <v>4200</v>
       </c>
       <c r="F159" t="n">
-        <v>100818.15</v>
+        <v>44254.77</v>
       </c>
       <c r="G159" t="n">
-        <v>5040.91</v>
+        <v>2086.33</v>
       </c>
       <c r="H159" t="n">
-        <v>95777.24000000001</v>
+        <v>29503.18</v>
       </c>
       <c r="I159" t="n">
-        <v>67212.10000000001</v>
+        <v>42168.44</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>95777.24000000001</v>
+        <v>42168.44</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E160" t="n">
-        <v>1200</v>
+        <v>15400</v>
       </c>
       <c r="F160" t="n">
-        <v>25604.61</v>
+        <v>507085.9</v>
       </c>
       <c r="G160" t="n">
-        <v>768.14</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>24836.47</v>
+        <v>322691.03</v>
       </c>
       <c r="I160" t="n">
-        <v>17496.48</v>
+        <v>507085.9</v>
       </c>
       <c r="J160" t="n">
-        <v>7450.94</v>
+        <v>152125.77</v>
       </c>
       <c r="K160" t="n">
-        <v>17385.53</v>
+        <v>354960.13</v>
       </c>
     </row>
     <row r="161">
@@ -6705,268 +6705,268 @@
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E161" t="n">
         <v>15400</v>
       </c>
       <c r="F161" t="n">
-        <v>225907.34</v>
+        <v>141984.05</v>
       </c>
       <c r="G161" t="n">
-        <v>18072.59</v>
+        <v>6693.65</v>
       </c>
       <c r="H161" t="n">
-        <v>207834.75</v>
+        <v>90353.49000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>143759.21</v>
+        <v>135290.4</v>
       </c>
       <c r="J161" t="n">
-        <v>103917.37</v>
+        <v>40587.12</v>
       </c>
       <c r="K161" t="n">
-        <v>103917.37</v>
+        <v>94703.28</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E162" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F162" t="n">
-        <v>315390.11</v>
+        <v>37932.66</v>
       </c>
       <c r="G162" t="n">
-        <v>37846.81</v>
+        <v>1072.97</v>
       </c>
       <c r="H162" t="n">
-        <v>277543.3</v>
+        <v>25920.65</v>
       </c>
       <c r="I162" t="n">
-        <v>208304.17</v>
+        <v>36859.69</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>11057.91</v>
       </c>
       <c r="K162" t="n">
-        <v>277543.3</v>
+        <v>25801.78</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E163" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F163" t="n">
-        <v>117621.18</v>
+        <v>19493.17</v>
       </c>
       <c r="G163" t="n">
-        <v>5881.06</v>
+        <v>551.39</v>
       </c>
       <c r="H163" t="n">
-        <v>111740.12</v>
+        <v>13171.06</v>
       </c>
       <c r="I163" t="n">
-        <v>78414.12</v>
+        <v>18941.78</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>9470.889999999999</v>
       </c>
       <c r="K163" t="n">
-        <v>111740.12</v>
+        <v>9470.889999999999</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E164" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="F164" t="n">
-        <v>178032.05</v>
+        <v>44254.77</v>
       </c>
       <c r="G164" t="n">
-        <v>8901.6</v>
+        <v>1251.8</v>
       </c>
       <c r="H164" t="n">
-        <v>169130.45</v>
+        <v>29503.18</v>
       </c>
       <c r="I164" t="n">
-        <v>118021.25</v>
+        <v>43002.97</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>169130.45</v>
+        <v>43002.97</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E165" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F165" t="n">
-        <v>36806.63</v>
+        <v>94041.39</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>36806.63</v>
+        <v>62694.26</v>
       </c>
       <c r="I165" t="n">
-        <v>25151.19</v>
+        <v>94041.39</v>
       </c>
       <c r="J165" t="n">
-        <v>18403.31</v>
+        <v>28212.42</v>
       </c>
       <c r="K165" t="n">
-        <v>18403.31</v>
+        <v>65828.97</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E166" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F166" t="n">
-        <v>106819.23</v>
+        <v>4280.6</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>121.08</v>
       </c>
       <c r="H166" t="n">
-        <v>106819.23</v>
+        <v>2897.63</v>
       </c>
       <c r="I166" t="n">
-        <v>70812.75</v>
+        <v>4159.52</v>
       </c>
       <c r="J166" t="n">
-        <v>53409.62</v>
+        <v>2079.76</v>
       </c>
       <c r="K166" t="n">
-        <v>53409.62</v>
+        <v>2079.76</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E167" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F167" t="n">
-        <v>61611.09</v>
+        <v>37932.66</v>
       </c>
       <c r="G167" t="n">
-        <v>1848.33</v>
+        <v>1788.28</v>
       </c>
       <c r="H167" t="n">
-        <v>59762.76</v>
+        <v>23707.91</v>
       </c>
       <c r="I167" t="n">
-        <v>39207.06</v>
+        <v>36144.38</v>
       </c>
       <c r="J167" t="n">
-        <v>29881.38</v>
+        <v>18072.19</v>
       </c>
       <c r="K167" t="n">
-        <v>29881.38</v>
+        <v>18072.19</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6978,229 +6978,229 @@
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E168" t="n">
         <v>8900</v>
       </c>
       <c r="F168" t="n">
-        <v>23737.61</v>
+        <v>293056.14</v>
       </c>
       <c r="G168" t="n">
-        <v>1186.88</v>
+        <v>8289.440000000001</v>
       </c>
       <c r="H168" t="n">
-        <v>22550.73</v>
+        <v>194273.17</v>
       </c>
       <c r="I168" t="n">
-        <v>15736.17</v>
+        <v>284766.7</v>
       </c>
       <c r="J168" t="n">
-        <v>11275.36</v>
+        <v>142383.35</v>
       </c>
       <c r="K168" t="n">
-        <v>11275.36</v>
+        <v>142383.35</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F169" t="n">
-        <v>22404.03</v>
+        <v>5531.85</v>
       </c>
       <c r="G169" t="n">
-        <v>2688.48</v>
+        <v>260.79</v>
       </c>
       <c r="H169" t="n">
-        <v>19715.55</v>
+        <v>3687.9</v>
       </c>
       <c r="I169" t="n">
-        <v>15309.42</v>
+        <v>5271.06</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>19715.55</v>
+        <v>5271.06</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E170" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F170" t="n">
-        <v>5601.01</v>
+        <v>21929.82</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>5601.01</v>
+        <v>14817.45</v>
       </c>
       <c r="I170" t="n">
-        <v>3734.01</v>
+        <v>21929.82</v>
       </c>
       <c r="J170" t="n">
-        <v>1680.3</v>
+        <v>6578.95</v>
       </c>
       <c r="K170" t="n">
-        <v>3920.71</v>
+        <v>15350.87</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E171" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F171" t="n">
-        <v>225507.26</v>
+        <v>31676.41</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1493.34</v>
       </c>
       <c r="H171" t="n">
-        <v>225507.26</v>
+        <v>21402.98</v>
       </c>
       <c r="I171" t="n">
-        <v>149493.58</v>
+        <v>30183.07</v>
       </c>
       <c r="J171" t="n">
-        <v>112753.63</v>
+        <v>9054.92</v>
       </c>
       <c r="K171" t="n">
-        <v>112753.63</v>
+        <v>21128.15</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E172" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F172" t="n">
-        <v>28671.83</v>
+        <v>44254.77</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1251.8</v>
       </c>
       <c r="H172" t="n">
-        <v>28671.83</v>
+        <v>27659.23</v>
       </c>
       <c r="I172" t="n">
-        <v>18936.74</v>
+        <v>43002.97</v>
       </c>
       <c r="J172" t="n">
-        <v>14335.91</v>
+        <v>21501.49</v>
       </c>
       <c r="K172" t="n">
-        <v>14335.91</v>
+        <v>21501.48</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D173" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E173" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F173" t="n">
-        <v>78414.12</v>
+        <v>105500.21</v>
       </c>
       <c r="G173" t="n">
-        <v>9409.690000000001</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>69004.42</v>
+        <v>69938.34</v>
       </c>
       <c r="I173" t="n">
-        <v>52276.08</v>
+        <v>105500.21</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>31650.06</v>
       </c>
       <c r="K173" t="n">
-        <v>69004.42</v>
+        <v>73850.14999999999</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7212,301 +7212,301 @@
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E174" t="n">
         <v>4200</v>
       </c>
       <c r="F174" t="n">
-        <v>44808.07</v>
+        <v>94041.39</v>
       </c>
       <c r="G174" t="n">
-        <v>2240.4</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>42567.66</v>
+        <v>62694.26</v>
       </c>
       <c r="I174" t="n">
-        <v>29872.04</v>
+        <v>94041.39</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>42567.66</v>
+        <v>94041.39</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E175" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F175" t="n">
-        <v>22404.03</v>
+        <v>211000.42</v>
       </c>
       <c r="G175" t="n">
-        <v>672.12</v>
+        <v>3978.93</v>
       </c>
       <c r="H175" t="n">
-        <v>21731.91</v>
+        <v>139876.68</v>
       </c>
       <c r="I175" t="n">
-        <v>14936.02</v>
+        <v>207021.49</v>
       </c>
       <c r="J175" t="n">
-        <v>6519.57</v>
+        <v>62106.45</v>
       </c>
       <c r="K175" t="n">
-        <v>15212.34</v>
+        <v>144915.04</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E176" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F176" t="n">
-        <v>102685.15</v>
+        <v>55318.46</v>
       </c>
       <c r="G176" t="n">
-        <v>5134.26</v>
+        <v>1564.75</v>
       </c>
       <c r="H176" t="n">
-        <v>97550.89999999999</v>
+        <v>36878.97</v>
       </c>
       <c r="I176" t="n">
-        <v>65345.1</v>
+        <v>53753.71</v>
       </c>
       <c r="J176" t="n">
-        <v>0</v>
+        <v>26876.85</v>
       </c>
       <c r="K176" t="n">
-        <v>97550.89999999999</v>
+        <v>26876.86</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F177" t="n">
-        <v>35606.41</v>
+        <v>3161.05</v>
       </c>
       <c r="G177" t="n">
-        <v>2848.51</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>32757.9</v>
+        <v>2160.05</v>
       </c>
       <c r="I177" t="n">
-        <v>23604.25</v>
+        <v>3161.05</v>
       </c>
       <c r="J177" t="n">
-        <v>16378.95</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>16378.95</v>
+        <v>3161.05</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E178" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F178" t="n">
-        <v>178032.05</v>
+        <v>12644.22</v>
       </c>
       <c r="G178" t="n">
-        <v>5340.96</v>
+        <v>357.66</v>
       </c>
       <c r="H178" t="n">
-        <v>172691.09</v>
+        <v>7902.64</v>
       </c>
       <c r="I178" t="n">
-        <v>118021.25</v>
+        <v>12286.56</v>
       </c>
       <c r="J178" t="n">
-        <v>86345.53999999999</v>
+        <v>3685.97</v>
       </c>
       <c r="K178" t="n">
-        <v>86345.53999999999</v>
+        <v>8600.59</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E179" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F179" t="n">
-        <v>166163.25</v>
+        <v>24366.47</v>
       </c>
       <c r="G179" t="n">
-        <v>13293.06</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>152870.19</v>
+        <v>16463.83</v>
       </c>
       <c r="I179" t="n">
-        <v>110153.16</v>
+        <v>24366.47</v>
       </c>
       <c r="J179" t="n">
-        <v>76435.09</v>
+        <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>76435.09</v>
+        <v>24366.47</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E180" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F180" t="n">
-        <v>4800.86</v>
+        <v>56042.87</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>4800.86</v>
+        <v>37866.8</v>
       </c>
       <c r="I180" t="n">
-        <v>3280.59</v>
+        <v>56042.87</v>
       </c>
       <c r="J180" t="n">
-        <v>0</v>
+        <v>16812.86</v>
       </c>
       <c r="K180" t="n">
-        <v>4800.86</v>
+        <v>39230.01</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E181" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F181" t="n">
-        <v>106419.16</v>
+        <v>14619.88</v>
       </c>
       <c r="G181" t="n">
-        <v>12770.3</v>
+        <v>413.54</v>
       </c>
       <c r="H181" t="n">
-        <v>93648.86</v>
+        <v>9878.299999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>70946.11</v>
+        <v>14206.34</v>
       </c>
       <c r="J181" t="n">
-        <v>28094.66</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>65554.2</v>
+        <v>14206.34</v>
       </c>
     </row>
   </sheetData>

--- a/demo_data/sectors/hizmet_yazilim/sales_ledger.xlsx
+++ b/demo_data/sectors/hizmet_yazilim/sales_ledger.xlsx
@@ -492,37 +492,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>2400</v>
+        <v>90000</v>
       </c>
       <c r="F2" t="n">
-        <v>56899.06</v>
+        <v>248370.1</v>
       </c>
       <c r="G2" t="n">
-        <v>1609.47</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>35561.87</v>
+        <v>85549.72</v>
       </c>
       <c r="I2" t="n">
-        <v>55289.59</v>
+        <v>248370.1</v>
       </c>
       <c r="J2" t="n">
-        <v>55289.59</v>
+        <v>248370.1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -531,37 +531,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>1850</v>
+        <v>75000</v>
       </c>
       <c r="F3" t="n">
-        <v>56042.87</v>
+        <v>109575.07</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>37866.8</v>
+        <v>37986.02</v>
       </c>
       <c r="I3" t="n">
-        <v>56042.87</v>
+        <v>109575.07</v>
       </c>
       <c r="J3" t="n">
-        <v>56042.87</v>
+        <v>109575.07</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,12 +570,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -585,22 +585,22 @@
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>21500</v>
+        <v>90000</v>
       </c>
       <c r="F4" t="n">
-        <v>396448.98</v>
+        <v>204540.13</v>
       </c>
       <c r="G4" t="n">
-        <v>7476.02</v>
+        <v>10105.02</v>
       </c>
       <c r="H4" t="n">
-        <v>261840.72</v>
+        <v>70452.71000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>388972.96</v>
+        <v>194435.11</v>
       </c>
       <c r="J4" t="n">
-        <v>388972.96</v>
+        <v>194435.11</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,37 +609,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>4200</v>
+        <v>125000</v>
       </c>
       <c r="F5" t="n">
-        <v>94041.39</v>
+        <v>243500.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>7217.87</v>
       </c>
       <c r="H5" t="n">
-        <v>62694.26</v>
+        <v>81816.05</v>
       </c>
       <c r="I5" t="n">
-        <v>94041.39</v>
+        <v>236282.28</v>
       </c>
       <c r="J5" t="n">
-        <v>94041.39</v>
+        <v>236282.28</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,37 +648,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>1200</v>
+        <v>90000</v>
       </c>
       <c r="F6" t="n">
-        <v>36352.13</v>
+        <v>204540.13</v>
       </c>
       <c r="G6" t="n">
-        <v>1713.77</v>
+        <v>6063.01</v>
       </c>
       <c r="H6" t="n">
-        <v>24840.62</v>
+        <v>70452.71000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>34638.36</v>
+        <v>198477.12</v>
       </c>
       <c r="J6" t="n">
-        <v>34638.36</v>
+        <v>198477.12</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>15400</v>
+        <v>75000</v>
       </c>
       <c r="F7" t="n">
-        <v>40566.87</v>
+        <v>158275.1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>25815.28</v>
+        <v>54868.7</v>
       </c>
       <c r="I7" t="n">
-        <v>40566.87</v>
+        <v>158275.1</v>
       </c>
       <c r="J7" t="n">
-        <v>40566.87</v>
+        <v>158275.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,37 +726,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>15400</v>
+        <v>48000</v>
       </c>
       <c r="F8" t="n">
-        <v>365101.85</v>
+        <v>62336.04</v>
       </c>
       <c r="G8" t="n">
-        <v>17212.24</v>
+        <v>1231.85</v>
       </c>
       <c r="H8" t="n">
-        <v>232337.54</v>
+        <v>20778.68</v>
       </c>
       <c r="I8" t="n">
-        <v>347889.61</v>
+        <v>61104.19</v>
       </c>
       <c r="J8" t="n">
-        <v>347889.61</v>
+        <v>61104.19</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,37 +765,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>1850</v>
+        <v>28000</v>
       </c>
       <c r="F9" t="n">
-        <v>14619.88</v>
+        <v>9090.67</v>
       </c>
       <c r="G9" t="n">
-        <v>275.69</v>
+        <v>449.11</v>
       </c>
       <c r="H9" t="n">
-        <v>9878.299999999999</v>
+        <v>3084.34</v>
       </c>
       <c r="I9" t="n">
-        <v>14344.19</v>
+        <v>8641.559999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>14344.19</v>
+        <v>8641.559999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,37 +804,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>1200</v>
+        <v>28000</v>
       </c>
       <c r="F10" t="n">
-        <v>30030.02</v>
+        <v>81816.05</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4042.01</v>
       </c>
       <c r="H10" t="n">
-        <v>20520.52</v>
+        <v>27759.02</v>
       </c>
       <c r="I10" t="n">
-        <v>30030.02</v>
+        <v>77774.03999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>30030.02</v>
+        <v>77774.03999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>2400</v>
+        <v>28000</v>
       </c>
       <c r="F11" t="n">
-        <v>9483.16</v>
+        <v>36362.69</v>
       </c>
       <c r="G11" t="n">
-        <v>178.83</v>
+        <v>718.58</v>
       </c>
       <c r="H11" t="n">
-        <v>5926.98</v>
+        <v>12337.34</v>
       </c>
       <c r="I11" t="n">
-        <v>9304.33</v>
+        <v>35644.11</v>
       </c>
       <c r="J11" t="n">
-        <v>9304.33</v>
+        <v>35644.11</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -882,37 +882,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>1200</v>
+        <v>75000</v>
       </c>
       <c r="F12" t="n">
-        <v>30030.02</v>
+        <v>36525.02</v>
       </c>
       <c r="G12" t="n">
-        <v>849.4400000000001</v>
+        <v>1082.68</v>
       </c>
       <c r="H12" t="n">
-        <v>20520.52</v>
+        <v>12662.01</v>
       </c>
       <c r="I12" t="n">
-        <v>29180.58</v>
+        <v>35442.34</v>
       </c>
       <c r="J12" t="n">
-        <v>29180.58</v>
+        <v>35442.34</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -921,37 +921,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>650</v>
+        <v>125000</v>
       </c>
       <c r="F13" t="n">
-        <v>11129.55</v>
+        <v>365250.23</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>7533.85</v>
+        <v>122724.08</v>
       </c>
       <c r="I13" t="n">
-        <v>11129.55</v>
+        <v>365250.23</v>
       </c>
       <c r="J13" t="n">
-        <v>11129.55</v>
+        <v>365250.23</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,37 +960,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F14" t="n">
-        <v>94041.39</v>
+        <v>158275.1</v>
       </c>
       <c r="G14" t="n">
-        <v>1773.38</v>
+        <v>7819.36</v>
       </c>
       <c r="H14" t="n">
-        <v>62694.26</v>
+        <v>54868.7</v>
       </c>
       <c r="I14" t="n">
-        <v>92268.00999999999</v>
+        <v>150455.74</v>
       </c>
       <c r="J14" t="n">
-        <v>92268.00999999999</v>
+        <v>150455.74</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>4200</v>
+        <v>125000</v>
       </c>
       <c r="F15" t="n">
-        <v>77445.85000000001</v>
+        <v>142041.76</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>7017.38</v>
       </c>
       <c r="H15" t="n">
-        <v>51630.56</v>
+        <v>47726.03</v>
       </c>
       <c r="I15" t="n">
-        <v>77445.85000000001</v>
+        <v>135024.38</v>
       </c>
       <c r="J15" t="n">
-        <v>77445.85000000001</v>
+        <v>135024.38</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>4200</v>
+        <v>28000</v>
       </c>
       <c r="F16" t="n">
-        <v>60850.31</v>
+        <v>31817.35</v>
       </c>
       <c r="G16" t="n">
-        <v>2868.71</v>
+        <v>628.76</v>
       </c>
       <c r="H16" t="n">
-        <v>40566.87</v>
+        <v>10795.17</v>
       </c>
       <c r="I16" t="n">
-        <v>57981.6</v>
+        <v>31188.59</v>
       </c>
       <c r="J16" t="n">
-        <v>57981.6</v>
+        <v>31188.59</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>2400</v>
+        <v>125000</v>
       </c>
       <c r="F17" t="n">
-        <v>79026.37</v>
+        <v>142041.76</v>
       </c>
       <c r="G17" t="n">
-        <v>1490.24</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>49391.48</v>
+        <v>47726.03</v>
       </c>
       <c r="I17" t="n">
-        <v>77536.13</v>
+        <v>142041.76</v>
       </c>
       <c r="J17" t="n">
-        <v>77536.13</v>
+        <v>142041.76</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>15400</v>
+        <v>90000</v>
       </c>
       <c r="F18" t="n">
-        <v>304251.54</v>
+        <v>233760.15</v>
       </c>
       <c r="G18" t="n">
-        <v>8606.120000000001</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>193614.62</v>
+        <v>80517.38</v>
       </c>
       <c r="I18" t="n">
-        <v>295645.42</v>
+        <v>233760.15</v>
       </c>
       <c r="J18" t="n">
-        <v>295645.42</v>
+        <v>233760.15</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,37 +1155,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>650</v>
+        <v>28000</v>
       </c>
       <c r="F19" t="n">
-        <v>15410.14</v>
+        <v>36362.69</v>
       </c>
       <c r="G19" t="n">
-        <v>435.89</v>
+        <v>1796.45</v>
       </c>
       <c r="H19" t="n">
-        <v>10431.48</v>
+        <v>12337.34</v>
       </c>
       <c r="I19" t="n">
-        <v>14974.25</v>
+        <v>34566.24</v>
       </c>
       <c r="J19" t="n">
-        <v>14974.25</v>
+        <v>34566.24</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>8900</v>
+        <v>75000</v>
       </c>
       <c r="F20" t="n">
-        <v>257889.4</v>
+        <v>158275.1</v>
       </c>
       <c r="G20" t="n">
-        <v>12157.85</v>
+        <v>4691.62</v>
       </c>
       <c r="H20" t="n">
-        <v>170960.39</v>
+        <v>54868.7</v>
       </c>
       <c r="I20" t="n">
-        <v>245731.55</v>
+        <v>153583.48</v>
       </c>
       <c r="J20" t="n">
-        <v>245731.55</v>
+        <v>153583.48</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,37 +1233,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>2400</v>
+        <v>75000</v>
       </c>
       <c r="F21" t="n">
-        <v>9483.16</v>
+        <v>109575.07</v>
       </c>
       <c r="G21" t="n">
-        <v>447.07</v>
+        <v>2165.36</v>
       </c>
       <c r="H21" t="n">
-        <v>5926.98</v>
+        <v>37986.02</v>
       </c>
       <c r="I21" t="n">
-        <v>9036.09</v>
+        <v>107409.71</v>
       </c>
       <c r="J21" t="n">
-        <v>9036.09</v>
+        <v>107409.71</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>1200</v>
+        <v>28000</v>
       </c>
       <c r="F22" t="n">
-        <v>36352.13</v>
+        <v>18181.34</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>538.9299999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>24840.62</v>
+        <v>6168.67</v>
       </c>
       <c r="I22" t="n">
-        <v>36352.13</v>
+        <v>17642.41</v>
       </c>
       <c r="J22" t="n">
-        <v>36352.13</v>
+        <v>17642.41</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>15400</v>
+        <v>48000</v>
       </c>
       <c r="F23" t="n">
-        <v>101417.18</v>
+        <v>93504.06</v>
       </c>
       <c r="G23" t="n">
-        <v>2868.71</v>
+        <v>1847.78</v>
       </c>
       <c r="H23" t="n">
-        <v>64538.21</v>
+        <v>31168.02</v>
       </c>
       <c r="I23" t="n">
-        <v>98548.47</v>
+        <v>91656.28</v>
       </c>
       <c r="J23" t="n">
-        <v>98548.47</v>
+        <v>91656.28</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>8900</v>
+        <v>125000</v>
       </c>
       <c r="F24" t="n">
-        <v>281333.89</v>
+        <v>385541.91</v>
       </c>
       <c r="G24" t="n">
-        <v>7957.87</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>186502.24</v>
+        <v>129542.08</v>
       </c>
       <c r="I24" t="n">
-        <v>273376.02</v>
+        <v>385541.91</v>
       </c>
       <c r="J24" t="n">
-        <v>273376.02</v>
+        <v>385541.91</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>650</v>
+        <v>125000</v>
       </c>
       <c r="F25" t="n">
-        <v>3424.48</v>
+        <v>182625.11</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>9022.34</v>
       </c>
       <c r="H25" t="n">
-        <v>2318.11</v>
+        <v>61362.04</v>
       </c>
       <c r="I25" t="n">
-        <v>3424.48</v>
+        <v>173602.77</v>
       </c>
       <c r="J25" t="n">
-        <v>3424.48</v>
+        <v>173602.77</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>15400</v>
+        <v>75000</v>
       </c>
       <c r="F26" t="n">
-        <v>304251.54</v>
+        <v>60875.04</v>
       </c>
       <c r="G26" t="n">
-        <v>5737.41</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>193614.62</v>
+        <v>21103.35</v>
       </c>
       <c r="I26" t="n">
-        <v>298514.13</v>
+        <v>60875.04</v>
       </c>
       <c r="J26" t="n">
-        <v>298514.13</v>
+        <v>60875.04</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>15400</v>
+        <v>48000</v>
       </c>
       <c r="F27" t="n">
-        <v>81133.74000000001</v>
+        <v>101296.06</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>5004.39</v>
       </c>
       <c r="H27" t="n">
-        <v>51630.56</v>
+        <v>33765.35</v>
       </c>
       <c r="I27" t="n">
-        <v>81133.74000000001</v>
+        <v>96291.67</v>
       </c>
       <c r="J27" t="n">
-        <v>81133.74000000001</v>
+        <v>96291.67</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>8900</v>
+        <v>28000</v>
       </c>
       <c r="F28" t="n">
-        <v>164111.44</v>
+        <v>81816.05</v>
       </c>
       <c r="G28" t="n">
-        <v>4642.09</v>
+        <v>1616.8</v>
       </c>
       <c r="H28" t="n">
-        <v>108792.98</v>
+        <v>27759.02</v>
       </c>
       <c r="I28" t="n">
-        <v>159469.35</v>
+        <v>80199.25</v>
       </c>
       <c r="J28" t="n">
-        <v>159469.35</v>
+        <v>80199.25</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,37 +1545,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>2400</v>
+        <v>28000</v>
       </c>
       <c r="F29" t="n">
-        <v>12644.22</v>
+        <v>72725.38</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2155.74</v>
       </c>
       <c r="H29" t="n">
-        <v>7902.64</v>
+        <v>24674.68</v>
       </c>
       <c r="I29" t="n">
-        <v>12644.22</v>
+        <v>70569.64</v>
       </c>
       <c r="J29" t="n">
-        <v>12644.22</v>
+        <v>70569.64</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>650</v>
+        <v>90000</v>
       </c>
       <c r="F30" t="n">
-        <v>15410.14</v>
+        <v>175320.11</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>10431.48</v>
+        <v>60388.04</v>
       </c>
       <c r="I30" t="n">
-        <v>15410.14</v>
+        <v>175320.11</v>
       </c>
       <c r="J30" t="n">
-        <v>15410.14</v>
+        <v>175320.11</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>650</v>
+        <v>90000</v>
       </c>
       <c r="F31" t="n">
-        <v>11129.55</v>
+        <v>262980.16</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>7795.3</v>
       </c>
       <c r="H31" t="n">
-        <v>7533.85</v>
+        <v>90582.06</v>
       </c>
       <c r="I31" t="n">
-        <v>11129.55</v>
+        <v>255184.86</v>
       </c>
       <c r="J31" t="n">
-        <v>11129.55</v>
+        <v>255184.86</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>2400</v>
+        <v>65000</v>
       </c>
       <c r="F32" t="n">
-        <v>41093.71</v>
+        <v>21103.35</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1042.58</v>
       </c>
       <c r="H32" t="n">
-        <v>25683.57</v>
+        <v>7142.67</v>
       </c>
       <c r="I32" t="n">
-        <v>41093.71</v>
+        <v>20060.77</v>
       </c>
       <c r="J32" t="n">
-        <v>41093.71</v>
+        <v>20060.77</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1200</v>
+        <v>125000</v>
       </c>
       <c r="F33" t="n">
-        <v>30030.02</v>
+        <v>40583.36</v>
       </c>
       <c r="G33" t="n">
-        <v>1415.73</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>20520.52</v>
+        <v>13636.01</v>
       </c>
       <c r="I33" t="n">
-        <v>28614.29</v>
+        <v>40583.36</v>
       </c>
       <c r="J33" t="n">
-        <v>28614.29</v>
+        <v>40583.36</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>2400</v>
+        <v>48000</v>
       </c>
       <c r="F34" t="n">
-        <v>18966.33</v>
+        <v>62336.04</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>11853.96</v>
+        <v>20778.68</v>
       </c>
       <c r="I34" t="n">
-        <v>18966.33</v>
+        <v>62336.04</v>
       </c>
       <c r="J34" t="n">
-        <v>18966.33</v>
+        <v>62336.04</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,37 +1779,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>15400</v>
+        <v>125000</v>
       </c>
       <c r="F35" t="n">
-        <v>182550.92</v>
+        <v>142041.76</v>
       </c>
       <c r="G35" t="n">
-        <v>5163.67</v>
+        <v>7017.38</v>
       </c>
       <c r="H35" t="n">
-        <v>116168.77</v>
+        <v>47726.03</v>
       </c>
       <c r="I35" t="n">
-        <v>177387.25</v>
+        <v>135024.38</v>
       </c>
       <c r="J35" t="n">
-        <v>177387.25</v>
+        <v>135024.38</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,37 +1818,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F36" t="n">
-        <v>33191.08</v>
+        <v>24350.02</v>
       </c>
       <c r="G36" t="n">
-        <v>938.85</v>
+        <v>1202.98</v>
       </c>
       <c r="H36" t="n">
-        <v>22127.38</v>
+        <v>8441.34</v>
       </c>
       <c r="I36" t="n">
-        <v>32252.23</v>
+        <v>23147.04</v>
       </c>
       <c r="J36" t="n">
-        <v>32252.23</v>
+        <v>23147.04</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,37 +1857,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>2400</v>
+        <v>90000</v>
       </c>
       <c r="F37" t="n">
-        <v>31610.55</v>
+        <v>233760.15</v>
       </c>
       <c r="G37" t="n">
-        <v>894.14</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>19756.59</v>
+        <v>80517.38</v>
       </c>
       <c r="I37" t="n">
-        <v>30716.41</v>
+        <v>233760.15</v>
       </c>
       <c r="J37" t="n">
-        <v>30716.41</v>
+        <v>233760.15</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1896,37 +1896,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E38" t="n">
-        <v>4200</v>
+        <v>65000</v>
       </c>
       <c r="F38" t="n">
-        <v>66382.14999999999</v>
+        <v>189930.12</v>
       </c>
       <c r="G38" t="n">
-        <v>1251.8</v>
+        <v>5629.94</v>
       </c>
       <c r="H38" t="n">
-        <v>44254.77</v>
+        <v>64284.04</v>
       </c>
       <c r="I38" t="n">
-        <v>65130.35</v>
+        <v>184300.18</v>
       </c>
       <c r="J38" t="n">
-        <v>65130.35</v>
+        <v>184300.18</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E39" t="n">
-        <v>21500</v>
+        <v>125000</v>
       </c>
       <c r="F39" t="n">
-        <v>566355.6800000001</v>
+        <v>344958.55</v>
       </c>
       <c r="G39" t="n">
-        <v>26700.08</v>
+        <v>6816.88</v>
       </c>
       <c r="H39" t="n">
-        <v>374058.17</v>
+        <v>115906.07</v>
       </c>
       <c r="I39" t="n">
-        <v>539655.6</v>
+        <v>338141.67</v>
       </c>
       <c r="J39" t="n">
-        <v>539655.6</v>
+        <v>338141.67</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E40" t="n">
-        <v>21500</v>
+        <v>125000</v>
       </c>
       <c r="F40" t="n">
-        <v>113271.14</v>
+        <v>344958.55</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>10225.32</v>
       </c>
       <c r="H40" t="n">
-        <v>74811.63</v>
+        <v>115906.07</v>
       </c>
       <c r="I40" t="n">
-        <v>113271.14</v>
+        <v>334733.23</v>
       </c>
       <c r="J40" t="n">
-        <v>113271.14</v>
+        <v>334733.23</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>1850</v>
+        <v>125000</v>
       </c>
       <c r="F41" t="n">
-        <v>31676.41</v>
+        <v>81166.72</v>
       </c>
       <c r="G41" t="n">
-        <v>597.34</v>
+        <v>4009.93</v>
       </c>
       <c r="H41" t="n">
-        <v>21402.98</v>
+        <v>27272.02</v>
       </c>
       <c r="I41" t="n">
-        <v>31079.07</v>
+        <v>77156.78999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>31079.07</v>
+        <v>77156.78999999999</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>2400</v>
+        <v>48000</v>
       </c>
       <c r="F42" t="n">
-        <v>34771.6</v>
+        <v>54544.03</v>
       </c>
       <c r="G42" t="n">
-        <v>983.5599999999999</v>
+        <v>2694.67</v>
       </c>
       <c r="H42" t="n">
-        <v>21732.25</v>
+        <v>18181.34</v>
       </c>
       <c r="I42" t="n">
-        <v>33788.04</v>
+        <v>51849.36</v>
       </c>
       <c r="J42" t="n">
-        <v>33788.04</v>
+        <v>51849.36</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>2400</v>
+        <v>75000</v>
       </c>
       <c r="F43" t="n">
-        <v>66382.14999999999</v>
+        <v>109575.07</v>
       </c>
       <c r="G43" t="n">
-        <v>3129.5</v>
+        <v>3248.04</v>
       </c>
       <c r="H43" t="n">
-        <v>41488.85</v>
+        <v>37986.02</v>
       </c>
       <c r="I43" t="n">
-        <v>63252.65</v>
+        <v>106327.03</v>
       </c>
       <c r="J43" t="n">
-        <v>63252.65</v>
+        <v>106327.03</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E44" t="n">
-        <v>15400</v>
+        <v>75000</v>
       </c>
       <c r="F44" t="n">
-        <v>223117.8</v>
+        <v>158275.1</v>
       </c>
       <c r="G44" t="n">
-        <v>10518.59</v>
+        <v>4691.62</v>
       </c>
       <c r="H44" t="n">
-        <v>141984.05</v>
+        <v>54868.7</v>
       </c>
       <c r="I44" t="n">
-        <v>212599.21</v>
+        <v>153583.48</v>
       </c>
       <c r="J44" t="n">
-        <v>212599.21</v>
+        <v>153583.48</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,37 +2169,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E45" t="n">
-        <v>1200</v>
+        <v>90000</v>
       </c>
       <c r="F45" t="n">
-        <v>25288.44</v>
+        <v>116880.07</v>
       </c>
       <c r="G45" t="n">
-        <v>476.88</v>
+        <v>2309.72</v>
       </c>
       <c r="H45" t="n">
-        <v>17280.43</v>
+        <v>40258.69</v>
       </c>
       <c r="I45" t="n">
-        <v>24811.56</v>
+        <v>114570.35</v>
       </c>
       <c r="J45" t="n">
-        <v>24811.56</v>
+        <v>114570.35</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>2400</v>
+        <v>90000</v>
       </c>
       <c r="F46" t="n">
-        <v>34771.6</v>
+        <v>29220.02</v>
       </c>
       <c r="G46" t="n">
-        <v>655.7</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>21732.25</v>
+        <v>10064.67</v>
       </c>
       <c r="I46" t="n">
-        <v>34115.9</v>
+        <v>29220.02</v>
       </c>
       <c r="J46" t="n">
-        <v>34115.9</v>
+        <v>29220.02</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E47" t="n">
-        <v>21500</v>
+        <v>28000</v>
       </c>
       <c r="F47" t="n">
-        <v>538037.9</v>
+        <v>59089.37</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2919.23</v>
       </c>
       <c r="H47" t="n">
-        <v>355355.26</v>
+        <v>20048.18</v>
       </c>
       <c r="I47" t="n">
-        <v>538037.9</v>
+        <v>56170.14</v>
       </c>
       <c r="J47" t="n">
-        <v>538037.9</v>
+        <v>56170.14</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>2400</v>
+        <v>125000</v>
       </c>
       <c r="F48" t="n">
-        <v>28449.49</v>
+        <v>20291.68</v>
       </c>
       <c r="G48" t="n">
-        <v>804.73</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>17780.93</v>
+        <v>6818</v>
       </c>
       <c r="I48" t="n">
-        <v>27644.76</v>
+        <v>20291.68</v>
       </c>
       <c r="J48" t="n">
-        <v>27644.76</v>
+        <v>20291.68</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E49" t="n">
-        <v>4200</v>
+        <v>28000</v>
       </c>
       <c r="F49" t="n">
-        <v>105105.08</v>
+        <v>63634.71</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1257.51</v>
       </c>
       <c r="H49" t="n">
-        <v>70070.05</v>
+        <v>21590.35</v>
       </c>
       <c r="I49" t="n">
-        <v>105105.08</v>
+        <v>62377.2</v>
       </c>
       <c r="J49" t="n">
-        <v>105105.08</v>
+        <v>62377.2</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,37 +2364,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>8900</v>
+        <v>65000</v>
       </c>
       <c r="F50" t="n">
-        <v>257889.4</v>
+        <v>21103.35</v>
       </c>
       <c r="G50" t="n">
-        <v>12157.85</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>170960.39</v>
+        <v>7142.67</v>
       </c>
       <c r="I50" t="n">
-        <v>245731.55</v>
+        <v>21103.35</v>
       </c>
       <c r="J50" t="n">
-        <v>245731.55</v>
+        <v>21103.35</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E51" t="n">
-        <v>21500</v>
+        <v>90000</v>
       </c>
       <c r="F51" t="n">
-        <v>651309.04</v>
+        <v>277590.17</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>8228.379999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>430166.9</v>
+        <v>95614.39</v>
       </c>
       <c r="I51" t="n">
-        <v>651309.04</v>
+        <v>269361.79</v>
       </c>
       <c r="J51" t="n">
-        <v>651309.04</v>
+        <v>269361.79</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,37 +2442,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>15400</v>
+        <v>125000</v>
       </c>
       <c r="F52" t="n">
-        <v>466519.03</v>
+        <v>60875.04</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1202.98</v>
       </c>
       <c r="H52" t="n">
-        <v>296875.75</v>
+        <v>20454.01</v>
       </c>
       <c r="I52" t="n">
-        <v>466519.03</v>
+        <v>59672.06</v>
       </c>
       <c r="J52" t="n">
-        <v>466519.03</v>
+        <v>59672.06</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,37 +2481,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="D53" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E53" t="n">
-        <v>2400</v>
+        <v>48000</v>
       </c>
       <c r="F53" t="n">
-        <v>69543.21000000001</v>
+        <v>85712.05</v>
       </c>
       <c r="G53" t="n">
-        <v>1967.11</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>43464.51</v>
+        <v>28570.68</v>
       </c>
       <c r="I53" t="n">
-        <v>67576.10000000001</v>
+        <v>85712.05</v>
       </c>
       <c r="J53" t="n">
-        <v>67576.10000000001</v>
+        <v>85712.05</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>15400</v>
+        <v>65000</v>
       </c>
       <c r="F54" t="n">
-        <v>162267.49</v>
+        <v>52758.37</v>
       </c>
       <c r="G54" t="n">
-        <v>3059.95</v>
+        <v>1563.87</v>
       </c>
       <c r="H54" t="n">
-        <v>103261.13</v>
+        <v>17856.68</v>
       </c>
       <c r="I54" t="n">
-        <v>159207.54</v>
+        <v>51194.5</v>
       </c>
       <c r="J54" t="n">
-        <v>159207.54</v>
+        <v>51194.5</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>8900</v>
+        <v>75000</v>
       </c>
       <c r="F55" t="n">
-        <v>269611.65</v>
+        <v>73050.05</v>
       </c>
       <c r="G55" t="n">
-        <v>7626.29</v>
+        <v>3608.94</v>
       </c>
       <c r="H55" t="n">
-        <v>178731.32</v>
+        <v>25324.02</v>
       </c>
       <c r="I55" t="n">
-        <v>261985.36</v>
+        <v>69441.11</v>
       </c>
       <c r="J55" t="n">
-        <v>261985.36</v>
+        <v>69441.11</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,37 +2598,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E56" t="n">
-        <v>2400</v>
+        <v>65000</v>
       </c>
       <c r="F56" t="n">
-        <v>9483.16</v>
+        <v>137171.75</v>
       </c>
       <c r="G56" t="n">
-        <v>268.24</v>
+        <v>6776.78</v>
       </c>
       <c r="H56" t="n">
-        <v>5926.98</v>
+        <v>46427.36</v>
       </c>
       <c r="I56" t="n">
-        <v>9214.92</v>
+        <v>130394.97</v>
       </c>
       <c r="J56" t="n">
-        <v>9214.92</v>
+        <v>130394.97</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>21500</v>
+        <v>28000</v>
       </c>
       <c r="F57" t="n">
-        <v>538037.9</v>
+        <v>22726.68</v>
       </c>
       <c r="G57" t="n">
-        <v>15219.05</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>355355.26</v>
+        <v>7710.84</v>
       </c>
       <c r="I57" t="n">
-        <v>522818.85</v>
+        <v>22726.68</v>
       </c>
       <c r="J57" t="n">
-        <v>522818.85</v>
+        <v>22726.68</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>2400</v>
+        <v>125000</v>
       </c>
       <c r="F58" t="n">
-        <v>56898.99</v>
+        <v>81166.72</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2405.96</v>
       </c>
       <c r="H58" t="n">
-        <v>35561.87</v>
+        <v>27272.02</v>
       </c>
       <c r="I58" t="n">
-        <v>56898.99</v>
+        <v>78760.75999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>56898.99</v>
+        <v>78760.75999999999</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E59" t="n">
-        <v>650</v>
+        <v>125000</v>
       </c>
       <c r="F59" t="n">
-        <v>19690.74</v>
+        <v>223208.47</v>
       </c>
       <c r="G59" t="n">
-        <v>928.29</v>
+        <v>11027.31</v>
       </c>
       <c r="H59" t="n">
-        <v>13329.12</v>
+        <v>74998.05</v>
       </c>
       <c r="I59" t="n">
-        <v>18762.45</v>
+        <v>212181.16</v>
       </c>
       <c r="J59" t="n">
-        <v>18762.45</v>
+        <v>212181.16</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,37 +2754,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F60" t="n">
-        <v>22127.38</v>
+        <v>12175.01</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>240.6</v>
       </c>
       <c r="H60" t="n">
-        <v>14751.59</v>
+        <v>4220.67</v>
       </c>
       <c r="I60" t="n">
-        <v>22127.38</v>
+        <v>11934.41</v>
       </c>
       <c r="J60" t="n">
-        <v>22127.38</v>
+        <v>11934.41</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,37 +2793,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E61" t="n">
-        <v>650</v>
+        <v>28000</v>
       </c>
       <c r="F61" t="n">
-        <v>5136.71</v>
+        <v>36362.69</v>
       </c>
       <c r="G61" t="n">
-        <v>242.16</v>
+        <v>718.58</v>
       </c>
       <c r="H61" t="n">
-        <v>3477.16</v>
+        <v>12337.34</v>
       </c>
       <c r="I61" t="n">
-        <v>4894.55</v>
+        <v>35644.11</v>
       </c>
       <c r="J61" t="n">
-        <v>4894.55</v>
+        <v>35644.11</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,37 +2832,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>2400</v>
+        <v>28000</v>
       </c>
       <c r="F62" t="n">
-        <v>79026.37</v>
+        <v>27272.02</v>
       </c>
       <c r="G62" t="n">
-        <v>1490.24</v>
+        <v>1347.34</v>
       </c>
       <c r="H62" t="n">
-        <v>49391.48</v>
+        <v>9253.01</v>
       </c>
       <c r="I62" t="n">
-        <v>77536.13</v>
+        <v>25924.68</v>
       </c>
       <c r="J62" t="n">
-        <v>77536.13</v>
+        <v>25924.68</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,37 +2871,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E63" t="n">
-        <v>2400</v>
+        <v>125000</v>
       </c>
       <c r="F63" t="n">
-        <v>12644.22</v>
+        <v>405833.59</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>8019.86</v>
       </c>
       <c r="H63" t="n">
-        <v>7902.64</v>
+        <v>136360.09</v>
       </c>
       <c r="I63" t="n">
-        <v>12644.22</v>
+        <v>397813.73</v>
       </c>
       <c r="J63" t="n">
-        <v>12644.22</v>
+        <v>397813.73</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,37 +2910,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>15400</v>
+        <v>90000</v>
       </c>
       <c r="F64" t="n">
-        <v>162267.49</v>
+        <v>43830.03</v>
       </c>
       <c r="G64" t="n">
-        <v>7649.88</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>103261.13</v>
+        <v>15097.01</v>
       </c>
       <c r="I64" t="n">
-        <v>154617.61</v>
+        <v>43830.03</v>
       </c>
       <c r="J64" t="n">
-        <v>154617.61</v>
+        <v>43830.03</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E65" t="n">
-        <v>1200</v>
+        <v>48000</v>
       </c>
       <c r="F65" t="n">
-        <v>23707.91</v>
+        <v>101296.06</v>
       </c>
       <c r="G65" t="n">
-        <v>447.07</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>16200.41</v>
+        <v>33765.35</v>
       </c>
       <c r="I65" t="n">
-        <v>23260.84</v>
+        <v>101296.06</v>
       </c>
       <c r="J65" t="n">
-        <v>23260.84</v>
+        <v>101296.06</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E66" t="n">
-        <v>21500</v>
+        <v>75000</v>
       </c>
       <c r="F66" t="n">
-        <v>707944.6</v>
+        <v>146100.09</v>
       </c>
       <c r="G66" t="n">
-        <v>33375.11</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>467572.72</v>
+        <v>50648.03</v>
       </c>
       <c r="I66" t="n">
-        <v>674569.49</v>
+        <v>146100.09</v>
       </c>
       <c r="J66" t="n">
-        <v>674569.49</v>
+        <v>146100.09</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E67" t="n">
-        <v>8900</v>
+        <v>125000</v>
       </c>
       <c r="F67" t="n">
-        <v>140666.95</v>
+        <v>202916.79</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>6014.9</v>
       </c>
       <c r="H67" t="n">
-        <v>93251.12</v>
+        <v>68180.03999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>140666.95</v>
+        <v>196901.89</v>
       </c>
       <c r="J67" t="n">
-        <v>140666.95</v>
+        <v>196901.89</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F68" t="n">
-        <v>55318.46</v>
+        <v>48700.03</v>
       </c>
       <c r="G68" t="n">
-        <v>1564.75</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>36878.97</v>
+        <v>16882.68</v>
       </c>
       <c r="I68" t="n">
-        <v>53753.71</v>
+        <v>48700.03</v>
       </c>
       <c r="J68" t="n">
-        <v>53753.71</v>
+        <v>48700.03</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E69" t="n">
-        <v>4200</v>
+        <v>48000</v>
       </c>
       <c r="F69" t="n">
-        <v>22127.38</v>
+        <v>109088.07</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>3233.61</v>
       </c>
       <c r="H69" t="n">
-        <v>14751.59</v>
+        <v>36362.69</v>
       </c>
       <c r="I69" t="n">
-        <v>22127.38</v>
+        <v>105854.46</v>
       </c>
       <c r="J69" t="n">
-        <v>22127.38</v>
+        <v>105854.46</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3144,37 +3144,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>15400</v>
+        <v>125000</v>
       </c>
       <c r="F70" t="n">
-        <v>223117.8</v>
+        <v>20291.68</v>
       </c>
       <c r="G70" t="n">
-        <v>6311.15</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>141984.05</v>
+        <v>6818</v>
       </c>
       <c r="I70" t="n">
-        <v>216806.65</v>
+        <v>20291.68</v>
       </c>
       <c r="J70" t="n">
-        <v>216806.65</v>
+        <v>20291.68</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>1200</v>
+        <v>65000</v>
       </c>
       <c r="F71" t="n">
-        <v>26868.97</v>
+        <v>31655.02</v>
       </c>
       <c r="G71" t="n">
-        <v>760.02</v>
+        <v>1563.87</v>
       </c>
       <c r="H71" t="n">
-        <v>18360.46</v>
+        <v>10714.01</v>
       </c>
       <c r="I71" t="n">
-        <v>26108.95</v>
+        <v>30091.15</v>
       </c>
       <c r="J71" t="n">
-        <v>26108.95</v>
+        <v>30091.15</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>21500</v>
+        <v>28000</v>
       </c>
       <c r="F72" t="n">
-        <v>113271.14</v>
+        <v>4545.34</v>
       </c>
       <c r="G72" t="n">
-        <v>3204.01</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>74811.63</v>
+        <v>1542.17</v>
       </c>
       <c r="I72" t="n">
-        <v>110067.13</v>
+        <v>4455.52</v>
       </c>
       <c r="J72" t="n">
-        <v>110067.13</v>
+        <v>4455.52</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,37 +3261,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>21500</v>
+        <v>28000</v>
       </c>
       <c r="F73" t="n">
-        <v>311495.63</v>
+        <v>13636.01</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>673.67</v>
       </c>
       <c r="H73" t="n">
-        <v>205731.99</v>
+        <v>4626.5</v>
       </c>
       <c r="I73" t="n">
-        <v>311495.63</v>
+        <v>12962.34</v>
       </c>
       <c r="J73" t="n">
-        <v>311495.63</v>
+        <v>12962.34</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,37 +3300,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="D74" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E74" t="n">
-        <v>1850</v>
+        <v>65000</v>
       </c>
       <c r="F74" t="n">
-        <v>56042.87</v>
+        <v>179378.45</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>37866.8</v>
+        <v>60712.7</v>
       </c>
       <c r="I74" t="n">
-        <v>56042.87</v>
+        <v>179378.45</v>
       </c>
       <c r="J74" t="n">
-        <v>56042.87</v>
+        <v>179378.45</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>650</v>
+        <v>48000</v>
       </c>
       <c r="F75" t="n">
-        <v>17978.5</v>
+        <v>38960.02</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>769.91</v>
       </c>
       <c r="H75" t="n">
-        <v>12170.06</v>
+        <v>12986.67</v>
       </c>
       <c r="I75" t="n">
-        <v>17978.5</v>
+        <v>38190.11</v>
       </c>
       <c r="J75" t="n">
-        <v>17978.5</v>
+        <v>38190.11</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E76" t="n">
-        <v>8900</v>
+        <v>75000</v>
       </c>
       <c r="F76" t="n">
-        <v>281333.89</v>
+        <v>194800.12</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>186502.24</v>
+        <v>67530.71000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>281333.89</v>
+        <v>194800.12</v>
       </c>
       <c r="J76" t="n">
-        <v>281333.89</v>
+        <v>194800.12</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,37 +3417,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E77" t="n">
-        <v>8900</v>
+        <v>48000</v>
       </c>
       <c r="F77" t="n">
-        <v>211000.42</v>
+        <v>109088.07</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>2155.74</v>
       </c>
       <c r="H77" t="n">
-        <v>139876.68</v>
+        <v>36362.69</v>
       </c>
       <c r="I77" t="n">
-        <v>211000.42</v>
+        <v>106932.33</v>
       </c>
       <c r="J77" t="n">
-        <v>211000.42</v>
+        <v>106932.33</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E78" t="n">
-        <v>2400</v>
+        <v>75000</v>
       </c>
       <c r="F78" t="n">
-        <v>47415.82</v>
+        <v>194800.12</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>29634.89</v>
+        <v>67530.71000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>47415.82</v>
+        <v>194800.12</v>
       </c>
       <c r="J78" t="n">
-        <v>47415.82</v>
+        <v>194800.12</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E79" t="n">
-        <v>2400</v>
+        <v>75000</v>
       </c>
       <c r="F79" t="n">
-        <v>66382.14999999999</v>
+        <v>97400.06</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2887.15</v>
       </c>
       <c r="H79" t="n">
-        <v>41488.85</v>
+        <v>33765.35</v>
       </c>
       <c r="I79" t="n">
-        <v>66382.14999999999</v>
+        <v>94512.91</v>
       </c>
       <c r="J79" t="n">
-        <v>66382.14999999999</v>
+        <v>94512.91</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,37 +3534,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>2400</v>
+        <v>28000</v>
       </c>
       <c r="F80" t="n">
-        <v>41093.71</v>
+        <v>18181.34</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>25683.57</v>
+        <v>6168.67</v>
       </c>
       <c r="I80" t="n">
-        <v>41093.71</v>
+        <v>18181.34</v>
       </c>
       <c r="J80" t="n">
-        <v>41093.71</v>
+        <v>18181.34</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E81" t="n">
-        <v>1200</v>
+        <v>125000</v>
       </c>
       <c r="F81" t="n">
-        <v>23707.91</v>
+        <v>263791.83</v>
       </c>
       <c r="G81" t="n">
-        <v>1117.68</v>
+        <v>5212.91</v>
       </c>
       <c r="H81" t="n">
-        <v>16200.41</v>
+        <v>88634.06</v>
       </c>
       <c r="I81" t="n">
-        <v>22590.23</v>
+        <v>258578.92</v>
       </c>
       <c r="J81" t="n">
-        <v>22590.23</v>
+        <v>258578.92</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E82" t="n">
-        <v>2400</v>
+        <v>75000</v>
       </c>
       <c r="F82" t="n">
-        <v>3161.05</v>
+        <v>182625.11</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>3608.94</v>
       </c>
       <c r="H82" t="n">
-        <v>1975.66</v>
+        <v>63310.04</v>
       </c>
       <c r="I82" t="n">
-        <v>3161.05</v>
+        <v>179016.17</v>
       </c>
       <c r="J82" t="n">
-        <v>3161.05</v>
+        <v>179016.17</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E83" t="n">
-        <v>15400</v>
+        <v>90000</v>
       </c>
       <c r="F83" t="n">
-        <v>507085.9</v>
+        <v>292200.18</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>322691.03</v>
+        <v>100646.73</v>
       </c>
       <c r="I83" t="n">
-        <v>507085.9</v>
+        <v>292200.18</v>
       </c>
       <c r="J83" t="n">
-        <v>507085.9</v>
+        <v>292200.18</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E84" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F84" t="n">
-        <v>99573.23</v>
+        <v>243500.15</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>66382.14999999999</v>
+        <v>84413.39</v>
       </c>
       <c r="I84" t="n">
-        <v>99573.23</v>
+        <v>243500.15</v>
       </c>
       <c r="J84" t="n">
-        <v>99573.23</v>
+        <v>243500.15</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E85" t="n">
-        <v>650</v>
+        <v>75000</v>
       </c>
       <c r="F85" t="n">
-        <v>5992.83</v>
+        <v>73050.05</v>
       </c>
       <c r="G85" t="n">
-        <v>169.51</v>
+        <v>2165.36</v>
       </c>
       <c r="H85" t="n">
-        <v>4056.69</v>
+        <v>25324.02</v>
       </c>
       <c r="I85" t="n">
-        <v>5823.32</v>
+        <v>70884.69</v>
       </c>
       <c r="J85" t="n">
-        <v>5823.32</v>
+        <v>70884.69</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E86" t="n">
-        <v>15400</v>
+        <v>75000</v>
       </c>
       <c r="F86" t="n">
-        <v>446235.59</v>
+        <v>194800.12</v>
       </c>
       <c r="G86" t="n">
-        <v>12622.31</v>
+        <v>9623.83</v>
       </c>
       <c r="H86" t="n">
-        <v>283968.11</v>
+        <v>67530.71000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>433613.28</v>
+        <v>185176.29</v>
       </c>
       <c r="J86" t="n">
-        <v>433613.28</v>
+        <v>185176.29</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,37 +3807,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E87" t="n">
-        <v>650</v>
+        <v>75000</v>
       </c>
       <c r="F87" t="n">
-        <v>17122.38</v>
+        <v>158275.1</v>
       </c>
       <c r="G87" t="n">
-        <v>484.33</v>
+        <v>3127.75</v>
       </c>
       <c r="H87" t="n">
-        <v>11590.53</v>
+        <v>54868.7</v>
       </c>
       <c r="I87" t="n">
-        <v>16638.05</v>
+        <v>155147.35</v>
       </c>
       <c r="J87" t="n">
-        <v>16638.05</v>
+        <v>155147.35</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>2400</v>
+        <v>75000</v>
       </c>
       <c r="F88" t="n">
-        <v>60060.04</v>
+        <v>48700.03</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2405.96</v>
       </c>
       <c r="H88" t="n">
-        <v>37537.53</v>
+        <v>16882.68</v>
       </c>
       <c r="I88" t="n">
-        <v>60060.04</v>
+        <v>46294.07</v>
       </c>
       <c r="J88" t="n">
-        <v>60060.04</v>
+        <v>46294.07</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,37 +3885,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E89" t="n">
-        <v>650</v>
+        <v>65000</v>
       </c>
       <c r="F89" t="n">
-        <v>12841.79</v>
+        <v>189930.12</v>
       </c>
       <c r="G89" t="n">
-        <v>605.41</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>8692.9</v>
+        <v>64284.04</v>
       </c>
       <c r="I89" t="n">
-        <v>12236.38</v>
+        <v>189930.12</v>
       </c>
       <c r="J89" t="n">
-        <v>12236.38</v>
+        <v>189930.12</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>15400</v>
+        <v>90000</v>
       </c>
       <c r="F90" t="n">
-        <v>405668.72</v>
+        <v>219150.14</v>
       </c>
       <c r="G90" t="n">
-        <v>19124.71</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>258152.82</v>
+        <v>75485.05</v>
       </c>
       <c r="I90" t="n">
-        <v>386544.01</v>
+        <v>219150.14</v>
       </c>
       <c r="J90" t="n">
-        <v>386544.01</v>
+        <v>219150.14</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>8900</v>
+        <v>75000</v>
       </c>
       <c r="F91" t="n">
-        <v>128944.7</v>
+        <v>36525.02</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1082.68</v>
       </c>
       <c r="H91" t="n">
-        <v>85480.19</v>
+        <v>12662.01</v>
       </c>
       <c r="I91" t="n">
-        <v>128944.7</v>
+        <v>35442.34</v>
       </c>
       <c r="J91" t="n">
-        <v>128944.7</v>
+        <v>35442.34</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E92" t="n">
-        <v>15400</v>
+        <v>48000</v>
       </c>
       <c r="F92" t="n">
-        <v>81133.74000000001</v>
+        <v>77920.05</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>51630.56</v>
+        <v>25973.35</v>
       </c>
       <c r="I92" t="n">
-        <v>81133.74000000001</v>
+        <v>77920.05</v>
       </c>
       <c r="J92" t="n">
-        <v>81133.74000000001</v>
+        <v>77920.05</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>8900</v>
+        <v>90000</v>
       </c>
       <c r="F93" t="n">
-        <v>199278.17</v>
+        <v>73050.05</v>
       </c>
       <c r="G93" t="n">
-        <v>5636.82</v>
+        <v>2165.36</v>
       </c>
       <c r="H93" t="n">
-        <v>132105.76</v>
+        <v>25161.68</v>
       </c>
       <c r="I93" t="n">
-        <v>193641.35</v>
+        <v>70884.69</v>
       </c>
       <c r="J93" t="n">
-        <v>193641.35</v>
+        <v>70884.69</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E94" t="n">
-        <v>8900</v>
+        <v>125000</v>
       </c>
       <c r="F94" t="n">
-        <v>222722.67</v>
+        <v>304375.19</v>
       </c>
       <c r="G94" t="n">
-        <v>6299.98</v>
+        <v>15037.24</v>
       </c>
       <c r="H94" t="n">
-        <v>147647.61</v>
+        <v>102270.06</v>
       </c>
       <c r="I94" t="n">
-        <v>216422.69</v>
+        <v>289337.95</v>
       </c>
       <c r="J94" t="n">
-        <v>216422.69</v>
+        <v>289337.95</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,37 +4119,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E95" t="n">
-        <v>8900</v>
+        <v>65000</v>
       </c>
       <c r="F95" t="n">
-        <v>187555.93</v>
+        <v>137171.75</v>
       </c>
       <c r="G95" t="n">
-        <v>8842.07</v>
+        <v>6776.78</v>
       </c>
       <c r="H95" t="n">
-        <v>124334.83</v>
+        <v>46427.36</v>
       </c>
       <c r="I95" t="n">
-        <v>178713.86</v>
+        <v>130394.97</v>
       </c>
       <c r="J95" t="n">
-        <v>178713.86</v>
+        <v>130394.97</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>8900</v>
+        <v>65000</v>
       </c>
       <c r="F96" t="n">
-        <v>211000.42</v>
+        <v>21103.35</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>417.03</v>
       </c>
       <c r="H96" t="n">
-        <v>139876.68</v>
+        <v>7142.67</v>
       </c>
       <c r="I96" t="n">
-        <v>211000.42</v>
+        <v>20686.32</v>
       </c>
       <c r="J96" t="n">
-        <v>211000.42</v>
+        <v>20686.32</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>15400</v>
+        <v>125000</v>
       </c>
       <c r="F97" t="n">
-        <v>101417.18</v>
+        <v>162333.43</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3207.94</v>
       </c>
       <c r="H97" t="n">
-        <v>64538.21</v>
+        <v>54544.03</v>
       </c>
       <c r="I97" t="n">
-        <v>101417.18</v>
+        <v>159125.49</v>
       </c>
       <c r="J97" t="n">
-        <v>101417.18</v>
+        <v>159125.49</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,12 +4236,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -4251,22 +4251,22 @@
         <v>20</v>
       </c>
       <c r="E98" t="n">
-        <v>21500</v>
+        <v>90000</v>
       </c>
       <c r="F98" t="n">
-        <v>566355.6800000001</v>
+        <v>292200.18</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>374058.17</v>
+        <v>100646.73</v>
       </c>
       <c r="I98" t="n">
-        <v>566355.6800000001</v>
+        <v>292200.18</v>
       </c>
       <c r="J98" t="n">
-        <v>566355.6800000001</v>
+        <v>292200.18</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E99" t="n">
-        <v>650</v>
+        <v>75000</v>
       </c>
       <c r="F99" t="n">
-        <v>856.12</v>
+        <v>170450.11</v>
       </c>
       <c r="G99" t="n">
-        <v>24.22</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>579.53</v>
+        <v>59089.37</v>
       </c>
       <c r="I99" t="n">
-        <v>831.9</v>
+        <v>170450.11</v>
       </c>
       <c r="J99" t="n">
-        <v>831.9</v>
+        <v>170450.11</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E100" t="n">
-        <v>1200</v>
+        <v>125000</v>
       </c>
       <c r="F100" t="n">
-        <v>20546.86</v>
+        <v>182625.11</v>
       </c>
       <c r="G100" t="n">
-        <v>968.65</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>14040.35</v>
+        <v>61362.04</v>
       </c>
       <c r="I100" t="n">
-        <v>19578.21</v>
+        <v>182625.11</v>
       </c>
       <c r="J100" t="n">
-        <v>19578.21</v>
+        <v>182625.11</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,37 +4353,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>45858</v>
       </c>
       <c r="D101" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E101" t="n">
-        <v>21500</v>
+        <v>28000</v>
       </c>
       <c r="F101" t="n">
-        <v>396448.98</v>
+        <v>54544.03</v>
       </c>
       <c r="G101" t="n">
-        <v>11214.04</v>
+        <v>1616.8</v>
       </c>
       <c r="H101" t="n">
-        <v>261840.72</v>
+        <v>18506.01</v>
       </c>
       <c r="I101" t="n">
-        <v>385234.94</v>
+        <v>52927.23</v>
       </c>
       <c r="J101" t="n">
-        <v>385234.94</v>
+        <v>52927.23</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,37 +4392,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E102" t="n">
-        <v>21500</v>
+        <v>90000</v>
       </c>
       <c r="F102" t="n">
-        <v>453084.55</v>
+        <v>277590.17</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>13713.96</v>
       </c>
       <c r="H102" t="n">
-        <v>299246.54</v>
+        <v>95614.39</v>
       </c>
       <c r="I102" t="n">
-        <v>453084.55</v>
+        <v>263876.21</v>
       </c>
       <c r="J102" t="n">
-        <v>453084.55</v>
+        <v>263876.21</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>1850</v>
+        <v>75000</v>
       </c>
       <c r="F103" t="n">
-        <v>60916.16</v>
+        <v>12175.01</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>360.89</v>
       </c>
       <c r="H103" t="n">
-        <v>41159.57</v>
+        <v>4220.67</v>
       </c>
       <c r="I103" t="n">
-        <v>60916.16</v>
+        <v>11814.12</v>
       </c>
       <c r="J103" t="n">
-        <v>60916.16</v>
+        <v>11814.12</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E104" t="n">
-        <v>1850</v>
+        <v>75000</v>
       </c>
       <c r="F104" t="n">
-        <v>21929.82</v>
+        <v>170450.11</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>14817.45</v>
+        <v>59089.37</v>
       </c>
       <c r="I104" t="n">
-        <v>21929.82</v>
+        <v>170450.11</v>
       </c>
       <c r="J104" t="n">
-        <v>21929.82</v>
+        <v>170450.11</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,37 +4509,37 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>15400</v>
+        <v>90000</v>
       </c>
       <c r="F105" t="n">
-        <v>121700.62</v>
+        <v>73050.05</v>
       </c>
       <c r="G105" t="n">
-        <v>3442.45</v>
+        <v>1443.57</v>
       </c>
       <c r="H105" t="n">
-        <v>77445.85000000001</v>
+        <v>25161.68</v>
       </c>
       <c r="I105" t="n">
-        <v>118258.17</v>
+        <v>71606.48</v>
       </c>
       <c r="J105" t="n">
-        <v>118258.17</v>
+        <v>71606.48</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E106" t="n">
-        <v>21500</v>
+        <v>75000</v>
       </c>
       <c r="F106" t="n">
-        <v>509720.11</v>
+        <v>182625.11</v>
       </c>
       <c r="G106" t="n">
-        <v>24030.08</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>336652.35</v>
+        <v>63310.04</v>
       </c>
       <c r="I106" t="n">
-        <v>485690.03</v>
+        <v>182625.11</v>
       </c>
       <c r="J106" t="n">
-        <v>485690.03</v>
+        <v>182625.11</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,37 +4587,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E107" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F107" t="n">
-        <v>49786.62</v>
+        <v>194800.12</v>
       </c>
       <c r="G107" t="n">
-        <v>2347.12</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>33191.08</v>
+        <v>67530.71000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>47439.5</v>
+        <v>194800.12</v>
       </c>
       <c r="J107" t="n">
-        <v>47439.5</v>
+        <v>194800.12</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E108" t="n">
-        <v>650</v>
+        <v>90000</v>
       </c>
       <c r="F108" t="n">
-        <v>15410.14</v>
+        <v>219150.14</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>4330.72</v>
       </c>
       <c r="H108" t="n">
-        <v>10431.48</v>
+        <v>75485.05</v>
       </c>
       <c r="I108" t="n">
-        <v>15410.14</v>
+        <v>214819.42</v>
       </c>
       <c r="J108" t="n">
-        <v>15410.14</v>
+        <v>214819.42</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>21500</v>
+        <v>75000</v>
       </c>
       <c r="F109" t="n">
-        <v>509720.11</v>
+        <v>24350.02</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>336652.35</v>
+        <v>8441.34</v>
       </c>
       <c r="I109" t="n">
-        <v>509720.11</v>
+        <v>24350.02</v>
       </c>
       <c r="J109" t="n">
-        <v>509720.11</v>
+        <v>24350.02</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E110" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F110" t="n">
-        <v>132764.31</v>
+        <v>48700.03</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>88509.53999999999</v>
+        <v>16882.68</v>
       </c>
       <c r="I110" t="n">
-        <v>132764.31</v>
+        <v>48700.03</v>
       </c>
       <c r="J110" t="n">
-        <v>132764.31</v>
+        <v>48700.03</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,37 +4743,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>1850</v>
+        <v>65000</v>
       </c>
       <c r="F111" t="n">
-        <v>36549.7</v>
+        <v>63310.04</v>
       </c>
       <c r="G111" t="n">
-        <v>689.23</v>
+        <v>3127.75</v>
       </c>
       <c r="H111" t="n">
-        <v>24695.74</v>
+        <v>21428.01</v>
       </c>
       <c r="I111" t="n">
-        <v>35860.47</v>
+        <v>60182.29</v>
       </c>
       <c r="J111" t="n">
-        <v>35860.47</v>
+        <v>60182.29</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E112" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F112" t="n">
-        <v>82977.69</v>
+        <v>219150.14</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>6496.09</v>
       </c>
       <c r="H112" t="n">
-        <v>55318.46</v>
+        <v>75972.05</v>
       </c>
       <c r="I112" t="n">
-        <v>82977.69</v>
+        <v>212654.05</v>
       </c>
       <c r="J112" t="n">
-        <v>82977.69</v>
+        <v>212654.05</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E113" t="n">
-        <v>1200</v>
+        <v>48000</v>
       </c>
       <c r="F113" t="n">
-        <v>11063.69</v>
+        <v>101296.06</v>
       </c>
       <c r="G113" t="n">
-        <v>521.58</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>7560.19</v>
+        <v>33765.35</v>
       </c>
       <c r="I113" t="n">
-        <v>10542.11</v>
+        <v>101296.06</v>
       </c>
       <c r="J113" t="n">
-        <v>10542.11</v>
+        <v>101296.06</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E114" t="n">
-        <v>650</v>
+        <v>90000</v>
       </c>
       <c r="F114" t="n">
-        <v>19690.74</v>
+        <v>204540.13</v>
       </c>
       <c r="G114" t="n">
-        <v>928.29</v>
+        <v>6063.01</v>
       </c>
       <c r="H114" t="n">
-        <v>13329.12</v>
+        <v>70452.71000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>18762.45</v>
+        <v>198477.12</v>
       </c>
       <c r="J114" t="n">
-        <v>18762.45</v>
+        <v>198477.12</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E115" t="n">
-        <v>2400</v>
+        <v>90000</v>
       </c>
       <c r="F115" t="n">
-        <v>18966.33</v>
+        <v>292200.18</v>
       </c>
       <c r="G115" t="n">
-        <v>894.14</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>11853.96</v>
+        <v>100646.73</v>
       </c>
       <c r="I115" t="n">
-        <v>18072.19</v>
+        <v>292200.18</v>
       </c>
       <c r="J115" t="n">
-        <v>18072.19</v>
+        <v>292200.18</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E116" t="n">
-        <v>1200</v>
+        <v>65000</v>
       </c>
       <c r="F116" t="n">
-        <v>11063.69</v>
+        <v>147723.43</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>4378.84</v>
       </c>
       <c r="H116" t="n">
-        <v>7560.19</v>
+        <v>49998.7</v>
       </c>
       <c r="I116" t="n">
-        <v>11063.69</v>
+        <v>143344.59</v>
       </c>
       <c r="J116" t="n">
-        <v>11063.69</v>
+        <v>143344.59</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4977,37 +4977,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E117" t="n">
-        <v>650</v>
+        <v>90000</v>
       </c>
       <c r="F117" t="n">
-        <v>15410.14</v>
+        <v>102270.06</v>
       </c>
       <c r="G117" t="n">
-        <v>290.6</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>10431.48</v>
+        <v>35226.36</v>
       </c>
       <c r="I117" t="n">
-        <v>15119.54</v>
+        <v>102270.06</v>
       </c>
       <c r="J117" t="n">
-        <v>15119.54</v>
+        <v>102270.06</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
-        <v>8900</v>
+        <v>90000</v>
       </c>
       <c r="F118" t="n">
-        <v>128944.7</v>
+        <v>43830.03</v>
       </c>
       <c r="G118" t="n">
-        <v>2431.57</v>
+        <v>2165.36</v>
       </c>
       <c r="H118" t="n">
-        <v>85480.19</v>
+        <v>15097.01</v>
       </c>
       <c r="I118" t="n">
-        <v>126513.13</v>
+        <v>41664.67</v>
       </c>
       <c r="J118" t="n">
-        <v>126513.13</v>
+        <v>41664.67</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E119" t="n">
-        <v>15400</v>
+        <v>65000</v>
       </c>
       <c r="F119" t="n">
-        <v>344818.41</v>
+        <v>63310.04</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1251.1</v>
       </c>
       <c r="H119" t="n">
-        <v>219429.9</v>
+        <v>21428.01</v>
       </c>
       <c r="I119" t="n">
-        <v>344818.41</v>
+        <v>62058.94</v>
       </c>
       <c r="J119" t="n">
-        <v>344818.41</v>
+        <v>62058.94</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E120" t="n">
-        <v>2400</v>
+        <v>48000</v>
       </c>
       <c r="F120" t="n">
-        <v>6322.11</v>
+        <v>116880.07</v>
       </c>
       <c r="G120" t="n">
-        <v>119.22</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>3951.32</v>
+        <v>38960.02</v>
       </c>
       <c r="I120" t="n">
-        <v>6202.89</v>
+        <v>116880.07</v>
       </c>
       <c r="J120" t="n">
-        <v>6202.89</v>
+        <v>116880.07</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E121" t="n">
-        <v>8900</v>
+        <v>90000</v>
       </c>
       <c r="F121" t="n">
-        <v>269611.65</v>
+        <v>233760.15</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>11548.6</v>
       </c>
       <c r="H121" t="n">
-        <v>178731.32</v>
+        <v>80517.38</v>
       </c>
       <c r="I121" t="n">
-        <v>269611.65</v>
+        <v>222211.55</v>
       </c>
       <c r="J121" t="n">
-        <v>269611.65</v>
+        <v>222211.55</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,37 +5172,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E122" t="n">
-        <v>8900</v>
+        <v>65000</v>
       </c>
       <c r="F122" t="n">
-        <v>269611.65</v>
+        <v>137171.75</v>
       </c>
       <c r="G122" t="n">
-        <v>5084.19</v>
+        <v>6776.78</v>
       </c>
       <c r="H122" t="n">
-        <v>178731.32</v>
+        <v>46427.36</v>
       </c>
       <c r="I122" t="n">
-        <v>264527.46</v>
+        <v>130394.97</v>
       </c>
       <c r="J122" t="n">
-        <v>264527.46</v>
+        <v>130394.97</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5211,37 +5211,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E123" t="n">
-        <v>1200</v>
+        <v>65000</v>
       </c>
       <c r="F123" t="n">
-        <v>39513.19</v>
+        <v>42206.69</v>
       </c>
       <c r="G123" t="n">
-        <v>1117.68</v>
+        <v>834.0700000000001</v>
       </c>
       <c r="H123" t="n">
-        <v>27000.68</v>
+        <v>14285.34</v>
       </c>
       <c r="I123" t="n">
-        <v>38395.51</v>
+        <v>41372.62</v>
       </c>
       <c r="J123" t="n">
-        <v>38395.51</v>
+        <v>41372.62</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,37 +5250,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E124" t="n">
-        <v>8900</v>
+        <v>28000</v>
       </c>
       <c r="F124" t="n">
-        <v>222722.67</v>
+        <v>90906.72</v>
       </c>
       <c r="G124" t="n">
-        <v>4199.99</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>147647.61</v>
+        <v>30843.35</v>
       </c>
       <c r="I124" t="n">
-        <v>218522.68</v>
+        <v>90906.72</v>
       </c>
       <c r="J124" t="n">
-        <v>218522.68</v>
+        <v>90906.72</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,37 +5289,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E125" t="n">
-        <v>2400</v>
+        <v>65000</v>
       </c>
       <c r="F125" t="n">
-        <v>41093.71</v>
+        <v>200481.79</v>
       </c>
       <c r="G125" t="n">
-        <v>1162.39</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>25683.57</v>
+        <v>67855.38</v>
       </c>
       <c r="I125" t="n">
-        <v>39931.32</v>
+        <v>200481.79</v>
       </c>
       <c r="J125" t="n">
-        <v>39931.32</v>
+        <v>200481.79</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E126" t="n">
-        <v>4200</v>
+        <v>75000</v>
       </c>
       <c r="F126" t="n">
-        <v>71914</v>
+        <v>48700.03</v>
       </c>
       <c r="G126" t="n">
-        <v>3390.29</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>47942.67</v>
+        <v>16882.68</v>
       </c>
       <c r="I126" t="n">
-        <v>68523.71000000001</v>
+        <v>48700.03</v>
       </c>
       <c r="J126" t="n">
-        <v>68523.71000000001</v>
+        <v>48700.03</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E127" t="n">
-        <v>15400</v>
+        <v>125000</v>
       </c>
       <c r="F127" t="n">
-        <v>466519.03</v>
+        <v>121750.08</v>
       </c>
       <c r="G127" t="n">
-        <v>8797.370000000001</v>
+        <v>2405.96</v>
       </c>
       <c r="H127" t="n">
-        <v>296875.75</v>
+        <v>40908.03</v>
       </c>
       <c r="I127" t="n">
-        <v>457721.66</v>
+        <v>119344.12</v>
       </c>
       <c r="J127" t="n">
-        <v>457721.66</v>
+        <v>119344.12</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E128" t="n">
-        <v>21500</v>
+        <v>65000</v>
       </c>
       <c r="F128" t="n">
-        <v>311495.63</v>
+        <v>137171.75</v>
       </c>
       <c r="G128" t="n">
-        <v>14685.05</v>
+        <v>4066.07</v>
       </c>
       <c r="H128" t="n">
-        <v>205731.99</v>
+        <v>46427.36</v>
       </c>
       <c r="I128" t="n">
-        <v>296810.58</v>
+        <v>133105.68</v>
       </c>
       <c r="J128" t="n">
-        <v>296810.58</v>
+        <v>133105.68</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E129" t="n">
-        <v>4200</v>
+        <v>65000</v>
       </c>
       <c r="F129" t="n">
-        <v>132764.31</v>
+        <v>137171.75</v>
       </c>
       <c r="G129" t="n">
-        <v>3755.4</v>
+        <v>4066.07</v>
       </c>
       <c r="H129" t="n">
-        <v>88509.53999999999</v>
+        <v>46427.36</v>
       </c>
       <c r="I129" t="n">
-        <v>129008.91</v>
+        <v>133105.68</v>
       </c>
       <c r="J129" t="n">
-        <v>129008.91</v>
+        <v>133105.68</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E130" t="n">
-        <v>650</v>
+        <v>28000</v>
       </c>
       <c r="F130" t="n">
-        <v>2568.36</v>
+        <v>81816.05</v>
       </c>
       <c r="G130" t="n">
-        <v>121.08</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>1738.58</v>
+        <v>27759.02</v>
       </c>
       <c r="I130" t="n">
-        <v>2447.28</v>
+        <v>81816.05</v>
       </c>
       <c r="J130" t="n">
-        <v>2447.28</v>
+        <v>81816.05</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,37 +5523,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E131" t="n">
-        <v>1200</v>
+        <v>28000</v>
       </c>
       <c r="F131" t="n">
-        <v>22127.38</v>
+        <v>45453.36</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>15120.38</v>
+        <v>15421.68</v>
       </c>
       <c r="I131" t="n">
-        <v>22127.38</v>
+        <v>45453.36</v>
       </c>
       <c r="J131" t="n">
-        <v>22127.38</v>
+        <v>45453.36</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,37 +5562,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>15400</v>
+        <v>75000</v>
       </c>
       <c r="F132" t="n">
-        <v>223117.8</v>
+        <v>182625.11</v>
       </c>
       <c r="G132" t="n">
-        <v>4207.44</v>
+        <v>9022.34</v>
       </c>
       <c r="H132" t="n">
-        <v>141984.05</v>
+        <v>63310.04</v>
       </c>
       <c r="I132" t="n">
-        <v>218910.36</v>
+        <v>173602.77</v>
       </c>
       <c r="J132" t="n">
-        <v>218910.36</v>
+        <v>173602.77</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>8900</v>
+        <v>75000</v>
       </c>
       <c r="F133" t="n">
-        <v>222722.67</v>
+        <v>12175.01</v>
       </c>
       <c r="G133" t="n">
-        <v>6299.98</v>
+        <v>360.89</v>
       </c>
       <c r="H133" t="n">
-        <v>147647.61</v>
+        <v>4220.67</v>
       </c>
       <c r="I133" t="n">
-        <v>216422.69</v>
+        <v>11814.12</v>
       </c>
       <c r="J133" t="n">
-        <v>216422.69</v>
+        <v>11814.12</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E134" t="n">
-        <v>650</v>
+        <v>48000</v>
       </c>
       <c r="F134" t="n">
-        <v>18834.62</v>
+        <v>101296.06</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>5004.39</v>
       </c>
       <c r="H134" t="n">
-        <v>12749.59</v>
+        <v>33765.35</v>
       </c>
       <c r="I134" t="n">
-        <v>18834.62</v>
+        <v>96291.67</v>
       </c>
       <c r="J134" t="n">
-        <v>18834.62</v>
+        <v>96291.67</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E135" t="n">
-        <v>4200</v>
+        <v>28000</v>
       </c>
       <c r="F135" t="n">
-        <v>116168.77</v>
+        <v>72725.38</v>
       </c>
       <c r="G135" t="n">
-        <v>3285.97</v>
+        <v>2155.74</v>
       </c>
       <c r="H135" t="n">
-        <v>77445.85000000001</v>
+        <v>24674.68</v>
       </c>
       <c r="I135" t="n">
-        <v>112882.8</v>
+        <v>70569.64</v>
       </c>
       <c r="J135" t="n">
-        <v>112882.8</v>
+        <v>70569.64</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,12 +5718,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -5733,22 +5733,22 @@
         <v>6</v>
       </c>
       <c r="E136" t="n">
-        <v>4200</v>
+        <v>28000</v>
       </c>
       <c r="F136" t="n">
-        <v>33191.08</v>
+        <v>27272.02</v>
       </c>
       <c r="G136" t="n">
-        <v>938.85</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>22127.38</v>
+        <v>9253.01</v>
       </c>
       <c r="I136" t="n">
-        <v>32252.23</v>
+        <v>27272.02</v>
       </c>
       <c r="J136" t="n">
-        <v>32252.23</v>
+        <v>27272.02</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5757,37 +5757,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E137" t="n">
-        <v>1850</v>
+        <v>48000</v>
       </c>
       <c r="F137" t="n">
-        <v>34113.05</v>
+        <v>77920.05</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>23049.36</v>
+        <v>25973.35</v>
       </c>
       <c r="I137" t="n">
-        <v>34113.05</v>
+        <v>77920.05</v>
       </c>
       <c r="J137" t="n">
-        <v>34113.05</v>
+        <v>77920.05</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5796,37 +5796,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E138" t="n">
-        <v>8900</v>
+        <v>48000</v>
       </c>
       <c r="F138" t="n">
-        <v>246167.16</v>
+        <v>140256.09</v>
       </c>
       <c r="G138" t="n">
-        <v>4642.09</v>
+        <v>2771.66</v>
       </c>
       <c r="H138" t="n">
-        <v>163189.46</v>
+        <v>46752.03</v>
       </c>
       <c r="I138" t="n">
-        <v>241525.07</v>
+        <v>137484.43</v>
       </c>
       <c r="J138" t="n">
-        <v>241525.07</v>
+        <v>137484.43</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5835,37 +5835,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E139" t="n">
-        <v>15400</v>
+        <v>28000</v>
       </c>
       <c r="F139" t="n">
-        <v>60850.31</v>
+        <v>86361.39</v>
       </c>
       <c r="G139" t="n">
-        <v>1147.48</v>
+        <v>2559.94</v>
       </c>
       <c r="H139" t="n">
-        <v>38722.92</v>
+        <v>29301.18</v>
       </c>
       <c r="I139" t="n">
-        <v>59702.83</v>
+        <v>83801.45</v>
       </c>
       <c r="J139" t="n">
-        <v>59702.83</v>
+        <v>83801.45</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5874,37 +5874,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E140" t="n">
-        <v>4200</v>
+        <v>65000</v>
       </c>
       <c r="F140" t="n">
-        <v>66382.14999999999</v>
+        <v>42206.69</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>834.0700000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>44254.77</v>
+        <v>14285.34</v>
       </c>
       <c r="I140" t="n">
-        <v>66382.14999999999</v>
+        <v>41372.62</v>
       </c>
       <c r="J140" t="n">
-        <v>66382.14999999999</v>
+        <v>41372.62</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5913,37 +5913,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>2400</v>
+        <v>65000</v>
       </c>
       <c r="F141" t="n">
-        <v>66382.14999999999</v>
+        <v>21103.35</v>
       </c>
       <c r="G141" t="n">
-        <v>1251.8</v>
+        <v>625.55</v>
       </c>
       <c r="H141" t="n">
-        <v>41488.85</v>
+        <v>7142.67</v>
       </c>
       <c r="I141" t="n">
-        <v>65130.35</v>
+        <v>20477.8</v>
       </c>
       <c r="J141" t="n">
-        <v>65130.35</v>
+        <v>20477.8</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5952,37 +5952,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E142" t="n">
-        <v>1200</v>
+        <v>28000</v>
       </c>
       <c r="F142" t="n">
-        <v>22127.38</v>
+        <v>18181.34</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>15120.38</v>
+        <v>6168.67</v>
       </c>
       <c r="I142" t="n">
-        <v>22127.38</v>
+        <v>18181.34</v>
       </c>
       <c r="J142" t="n">
-        <v>22127.38</v>
+        <v>18181.34</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5991,37 +5991,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E143" t="n">
-        <v>4200</v>
+        <v>125000</v>
       </c>
       <c r="F143" t="n">
-        <v>5531.85</v>
+        <v>304375.19</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>6014.9</v>
       </c>
       <c r="H143" t="n">
-        <v>3687.9</v>
+        <v>102270.06</v>
       </c>
       <c r="I143" t="n">
-        <v>5531.85</v>
+        <v>298360.29</v>
       </c>
       <c r="J143" t="n">
-        <v>5531.85</v>
+        <v>298360.29</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6030,37 +6030,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E144" t="n">
-        <v>4200</v>
+        <v>125000</v>
       </c>
       <c r="F144" t="n">
-        <v>27659.23</v>
+        <v>304375.19</v>
       </c>
       <c r="G144" t="n">
-        <v>1303.96</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>18439.49</v>
+        <v>102270.06</v>
       </c>
       <c r="I144" t="n">
-        <v>26355.27</v>
+        <v>304375.19</v>
       </c>
       <c r="J144" t="n">
-        <v>26355.27</v>
+        <v>304375.19</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6069,37 +6069,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E145" t="n">
-        <v>21500</v>
+        <v>48000</v>
       </c>
       <c r="F145" t="n">
-        <v>28317.78</v>
+        <v>148048.09</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>2925.64</v>
       </c>
       <c r="H145" t="n">
-        <v>18702.91</v>
+        <v>49349.36</v>
       </c>
       <c r="I145" t="n">
-        <v>28317.78</v>
+        <v>145122.45</v>
       </c>
       <c r="J145" t="n">
-        <v>28317.78</v>
+        <v>145122.45</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6108,37 +6108,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E146" t="n">
-        <v>650</v>
+        <v>48000</v>
       </c>
       <c r="F146" t="n">
-        <v>3424.48</v>
+        <v>155840.1</v>
       </c>
       <c r="G146" t="n">
-        <v>96.87</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>2318.11</v>
+        <v>51946.7</v>
       </c>
       <c r="I146" t="n">
-        <v>3327.61</v>
+        <v>155840.1</v>
       </c>
       <c r="J146" t="n">
-        <v>3327.61</v>
+        <v>155840.1</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6147,792 +6147,792 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E147" t="n">
-        <v>8900</v>
+        <v>48000</v>
       </c>
       <c r="F147" t="n">
-        <v>187555.93</v>
+        <v>15584.01</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>769.91</v>
       </c>
       <c r="H147" t="n">
-        <v>124334.83</v>
+        <v>5194.67</v>
       </c>
       <c r="I147" t="n">
-        <v>187555.93</v>
+        <v>14814.1</v>
       </c>
       <c r="J147" t="n">
-        <v>56266.78</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>131289.15</v>
+        <v>14814.1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E148" t="n">
-        <v>2400</v>
+        <v>65000</v>
       </c>
       <c r="F148" t="n">
-        <v>9483.16</v>
+        <v>94965.06</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>4691.62</v>
       </c>
       <c r="H148" t="n">
-        <v>5926.98</v>
+        <v>32142.02</v>
       </c>
       <c r="I148" t="n">
-        <v>9483.16</v>
+        <v>90273.44</v>
       </c>
       <c r="J148" t="n">
-        <v>4741.58</v>
+        <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>4741.58</v>
+        <v>90273.44</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E149" t="n">
-        <v>650</v>
+        <v>75000</v>
       </c>
       <c r="F149" t="n">
-        <v>10273.43</v>
+        <v>121750.08</v>
       </c>
       <c r="G149" t="n">
-        <v>193.73</v>
+        <v>2405.96</v>
       </c>
       <c r="H149" t="n">
-        <v>6954.32</v>
+        <v>42206.69</v>
       </c>
       <c r="I149" t="n">
-        <v>10079.7</v>
+        <v>119344.12</v>
       </c>
       <c r="J149" t="n">
-        <v>5039.85</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>5039.85</v>
+        <v>119344.12</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E150" t="n">
-        <v>2400</v>
+        <v>65000</v>
       </c>
       <c r="F150" t="n">
-        <v>79026.37</v>
+        <v>42206.69</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>49391.48</v>
+        <v>14285.34</v>
       </c>
       <c r="I150" t="n">
-        <v>79026.37</v>
+        <v>42206.69</v>
       </c>
       <c r="J150" t="n">
-        <v>39513.18</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>39513.19</v>
+        <v>42206.69</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E151" t="n">
-        <v>8900</v>
+        <v>125000</v>
       </c>
       <c r="F151" t="n">
-        <v>35166.74</v>
+        <v>182625.11</v>
       </c>
       <c r="G151" t="n">
-        <v>1657.89</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>23312.78</v>
+        <v>61362.04</v>
       </c>
       <c r="I151" t="n">
-        <v>33508.85</v>
+        <v>182625.11</v>
       </c>
       <c r="J151" t="n">
-        <v>10052.65</v>
+        <v>91312.55</v>
       </c>
       <c r="K151" t="n">
-        <v>23456.2</v>
+        <v>91312.56</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E152" t="n">
-        <v>1850</v>
+        <v>48000</v>
       </c>
       <c r="F152" t="n">
-        <v>48732.93</v>
+        <v>38960.02</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>769.91</v>
       </c>
       <c r="H152" t="n">
-        <v>32927.66</v>
+        <v>12986.67</v>
       </c>
       <c r="I152" t="n">
-        <v>48732.93</v>
+        <v>38190.11</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>19095.06</v>
       </c>
       <c r="K152" t="n">
-        <v>48732.93</v>
+        <v>19095.05</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E153" t="n">
-        <v>650</v>
+        <v>90000</v>
       </c>
       <c r="F153" t="n">
-        <v>20546.86</v>
+        <v>189930.12</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>5629.94</v>
       </c>
       <c r="H153" t="n">
-        <v>13908.64</v>
+        <v>65420.37</v>
       </c>
       <c r="I153" t="n">
-        <v>20546.86</v>
+        <v>184300.18</v>
       </c>
       <c r="J153" t="n">
-        <v>6164.06</v>
+        <v>55290.05</v>
       </c>
       <c r="K153" t="n">
-        <v>14382.8</v>
+        <v>129010.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E154" t="n">
-        <v>8900</v>
+        <v>65000</v>
       </c>
       <c r="F154" t="n">
-        <v>164111.44</v>
+        <v>94965.06</v>
       </c>
       <c r="G154" t="n">
-        <v>7736.82</v>
+        <v>2814.97</v>
       </c>
       <c r="H154" t="n">
-        <v>108792.98</v>
+        <v>32142.02</v>
       </c>
       <c r="I154" t="n">
-        <v>156374.62</v>
+        <v>92150.09</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>27645.03</v>
       </c>
       <c r="K154" t="n">
-        <v>156374.62</v>
+        <v>64505.06</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E155" t="n">
-        <v>21500</v>
+        <v>28000</v>
       </c>
       <c r="F155" t="n">
-        <v>198224.49</v>
+        <v>13636.01</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>130920.36</v>
+        <v>4626.5</v>
       </c>
       <c r="I155" t="n">
-        <v>198224.49</v>
+        <v>13636.01</v>
       </c>
       <c r="J155" t="n">
-        <v>99112.24000000001</v>
+        <v>4090.8</v>
       </c>
       <c r="K155" t="n">
-        <v>99112.25</v>
+        <v>9545.209999999999</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E156" t="n">
-        <v>4200</v>
+        <v>65000</v>
       </c>
       <c r="F156" t="n">
-        <v>27659.23</v>
+        <v>94965.06</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1876.65</v>
       </c>
       <c r="H156" t="n">
-        <v>18439.49</v>
+        <v>32142.02</v>
       </c>
       <c r="I156" t="n">
-        <v>27659.23</v>
+        <v>93088.41</v>
       </c>
       <c r="J156" t="n">
-        <v>8297.77</v>
+        <v>27926.52</v>
       </c>
       <c r="K156" t="n">
-        <v>19361.46</v>
+        <v>65161.89</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E157" t="n">
-        <v>2400</v>
+        <v>28000</v>
       </c>
       <c r="F157" t="n">
-        <v>37932.66</v>
+        <v>49998.7</v>
       </c>
       <c r="G157" t="n">
-        <v>1072.97</v>
+        <v>2470.12</v>
       </c>
       <c r="H157" t="n">
-        <v>23707.91</v>
+        <v>16963.84</v>
       </c>
       <c r="I157" t="n">
-        <v>36859.69</v>
+        <v>47528.58</v>
       </c>
       <c r="J157" t="n">
-        <v>18429.85</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>18429.84</v>
+        <v>47528.58</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E158" t="n">
-        <v>8900</v>
+        <v>90000</v>
       </c>
       <c r="F158" t="n">
-        <v>93777.96000000001</v>
+        <v>43830.03</v>
       </c>
       <c r="G158" t="n">
-        <v>1768.41</v>
+        <v>1299.22</v>
       </c>
       <c r="H158" t="n">
-        <v>62167.41</v>
+        <v>15097.01</v>
       </c>
       <c r="I158" t="n">
-        <v>92009.55</v>
+        <v>42530.81</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>92009.55</v>
+        <v>42530.81</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E159" t="n">
-        <v>4200</v>
+        <v>125000</v>
       </c>
       <c r="F159" t="n">
-        <v>44254.77</v>
+        <v>365250.23</v>
       </c>
       <c r="G159" t="n">
-        <v>2086.33</v>
+        <v>10826.81</v>
       </c>
       <c r="H159" t="n">
-        <v>29503.18</v>
+        <v>122724.08</v>
       </c>
       <c r="I159" t="n">
-        <v>42168.44</v>
+        <v>354423.42</v>
       </c>
       <c r="J159" t="n">
-        <v>0</v>
+        <v>106327.03</v>
       </c>
       <c r="K159" t="n">
-        <v>42168.44</v>
+        <v>248096.39</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Kurumsal Müşteri D - Nova</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E160" t="n">
-        <v>15400</v>
+        <v>28000</v>
       </c>
       <c r="F160" t="n">
-        <v>507085.9</v>
+        <v>31817.35</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>943.14</v>
       </c>
       <c r="H160" t="n">
-        <v>322691.03</v>
+        <v>10795.17</v>
       </c>
       <c r="I160" t="n">
-        <v>507085.9</v>
+        <v>30874.21</v>
       </c>
       <c r="J160" t="n">
-        <v>152125.77</v>
+        <v>15437.1</v>
       </c>
       <c r="K160" t="n">
-        <v>354960.13</v>
+        <v>15437.11</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E161" t="n">
-        <v>15400</v>
+        <v>75000</v>
       </c>
       <c r="F161" t="n">
-        <v>141984.05</v>
+        <v>121750.08</v>
       </c>
       <c r="G161" t="n">
-        <v>6693.65</v>
+        <v>2405.96</v>
       </c>
       <c r="H161" t="n">
-        <v>90353.49000000001</v>
+        <v>42206.69</v>
       </c>
       <c r="I161" t="n">
-        <v>135290.4</v>
+        <v>119344.12</v>
       </c>
       <c r="J161" t="n">
-        <v>40587.12</v>
+        <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>94703.28</v>
+        <v>119344.12</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E162" t="n">
-        <v>1200</v>
+        <v>65000</v>
       </c>
       <c r="F162" t="n">
-        <v>37932.66</v>
+        <v>168826.77</v>
       </c>
       <c r="G162" t="n">
-        <v>1072.97</v>
+        <v>3336.26</v>
       </c>
       <c r="H162" t="n">
-        <v>25920.65</v>
+        <v>57141.37</v>
       </c>
       <c r="I162" t="n">
-        <v>36859.69</v>
+        <v>165490.51</v>
       </c>
       <c r="J162" t="n">
-        <v>11057.91</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>25801.78</v>
+        <v>165490.51</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E163" t="n">
-        <v>1850</v>
+        <v>125000</v>
       </c>
       <c r="F163" t="n">
-        <v>19493.17</v>
+        <v>81166.72</v>
       </c>
       <c r="G163" t="n">
-        <v>551.39</v>
+        <v>2405.96</v>
       </c>
       <c r="H163" t="n">
-        <v>13171.06</v>
+        <v>27272.02</v>
       </c>
       <c r="I163" t="n">
-        <v>18941.78</v>
+        <v>78760.75999999999</v>
       </c>
       <c r="J163" t="n">
-        <v>9470.889999999999</v>
+        <v>39380.38</v>
       </c>
       <c r="K163" t="n">
-        <v>9470.889999999999</v>
+        <v>39380.38</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E164" t="n">
-        <v>4200</v>
+        <v>125000</v>
       </c>
       <c r="F164" t="n">
-        <v>44254.77</v>
+        <v>121750.08</v>
       </c>
       <c r="G164" t="n">
-        <v>1251.8</v>
+        <v>3608.94</v>
       </c>
       <c r="H164" t="n">
-        <v>29503.18</v>
+        <v>40908.03</v>
       </c>
       <c r="I164" t="n">
-        <v>43002.97</v>
+        <v>118141.14</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>59070.57</v>
       </c>
       <c r="K164" t="n">
-        <v>43002.97</v>
+        <v>59070.57</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E165" t="n">
-        <v>4200</v>
+        <v>125000</v>
       </c>
       <c r="F165" t="n">
-        <v>94041.39</v>
+        <v>284083.51</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>62694.26</v>
+        <v>95452.06</v>
       </c>
       <c r="I165" t="n">
-        <v>94041.39</v>
+        <v>284083.51</v>
       </c>
       <c r="J165" t="n">
-        <v>28212.42</v>
+        <v>142041.76</v>
       </c>
       <c r="K165" t="n">
-        <v>65828.97</v>
+        <v>142041.75</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E166" t="n">
-        <v>650</v>
+        <v>90000</v>
       </c>
       <c r="F166" t="n">
-        <v>4280.6</v>
+        <v>146100.09</v>
       </c>
       <c r="G166" t="n">
-        <v>121.08</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>2897.63</v>
+        <v>50323.36</v>
       </c>
       <c r="I166" t="n">
-        <v>4159.52</v>
+        <v>146100.09</v>
       </c>
       <c r="J166" t="n">
-        <v>2079.76</v>
+        <v>73050.03999999999</v>
       </c>
       <c r="K166" t="n">
-        <v>2079.76</v>
+        <v>73050.05</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
@@ -6942,571 +6942,571 @@
         <v>12</v>
       </c>
       <c r="E167" t="n">
-        <v>2400</v>
+        <v>125000</v>
       </c>
       <c r="F167" t="n">
-        <v>37932.66</v>
+        <v>243500.15</v>
       </c>
       <c r="G167" t="n">
-        <v>1788.28</v>
+        <v>4811.92</v>
       </c>
       <c r="H167" t="n">
-        <v>23707.91</v>
+        <v>81816.05</v>
       </c>
       <c r="I167" t="n">
-        <v>36144.38</v>
+        <v>238688.23</v>
       </c>
       <c r="J167" t="n">
-        <v>18072.19</v>
+        <v>119344.12</v>
       </c>
       <c r="K167" t="n">
-        <v>18072.19</v>
+        <v>119344.11</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Entegrasyon &amp; API Mühendisliği</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E168" t="n">
-        <v>8900</v>
+        <v>75000</v>
       </c>
       <c r="F168" t="n">
-        <v>293056.14</v>
+        <v>73050.05</v>
       </c>
       <c r="G168" t="n">
-        <v>8289.440000000001</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>194273.17</v>
+        <v>25324.02</v>
       </c>
       <c r="I168" t="n">
-        <v>284766.7</v>
+        <v>73050.05</v>
       </c>
       <c r="J168" t="n">
-        <v>142383.35</v>
+        <v>21915.01</v>
       </c>
       <c r="K168" t="n">
-        <v>142383.35</v>
+        <v>51135.04</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E169" t="n">
-        <v>4200</v>
+        <v>90000</v>
       </c>
       <c r="F169" t="n">
-        <v>5531.85</v>
+        <v>146100.09</v>
       </c>
       <c r="G169" t="n">
-        <v>260.79</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>3687.9</v>
+        <v>50323.36</v>
       </c>
       <c r="I169" t="n">
-        <v>5271.06</v>
+        <v>146100.09</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>73050.03999999999</v>
       </c>
       <c r="K169" t="n">
-        <v>5271.06</v>
+        <v>73050.05</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E170" t="n">
-        <v>1850</v>
+        <v>90000</v>
       </c>
       <c r="F170" t="n">
-        <v>21929.82</v>
+        <v>43830.03</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>14817.45</v>
+        <v>15097.01</v>
       </c>
       <c r="I170" t="n">
-        <v>21929.82</v>
+        <v>43830.03</v>
       </c>
       <c r="J170" t="n">
-        <v>6578.95</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>15350.87</v>
+        <v>43830.03</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E171" t="n">
-        <v>1850</v>
+        <v>48000</v>
       </c>
       <c r="F171" t="n">
-        <v>31676.41</v>
+        <v>124672.08</v>
       </c>
       <c r="G171" t="n">
-        <v>1493.34</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>21402.98</v>
+        <v>41557.36</v>
       </c>
       <c r="I171" t="n">
-        <v>30183.07</v>
+        <v>124672.08</v>
       </c>
       <c r="J171" t="n">
-        <v>9054.92</v>
+        <v>62336.04</v>
       </c>
       <c r="K171" t="n">
-        <v>21128.15</v>
+        <v>62336.04</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E172" t="n">
-        <v>2400</v>
+        <v>65000</v>
       </c>
       <c r="F172" t="n">
-        <v>44254.77</v>
+        <v>84413.39</v>
       </c>
       <c r="G172" t="n">
-        <v>1251.8</v>
+        <v>4170.33</v>
       </c>
       <c r="H172" t="n">
-        <v>27659.23</v>
+        <v>28570.68</v>
       </c>
       <c r="I172" t="n">
-        <v>43002.97</v>
+        <v>80243.06</v>
       </c>
       <c r="J172" t="n">
-        <v>21501.49</v>
+        <v>24072.92</v>
       </c>
       <c r="K172" t="n">
-        <v>21501.48</v>
+        <v>56170.14</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ulusal Hesap H - Nova</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D173" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>8900</v>
+        <v>125000</v>
       </c>
       <c r="F173" t="n">
-        <v>105500.21</v>
+        <v>20291.68</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>400.99</v>
       </c>
       <c r="H173" t="n">
-        <v>69938.34</v>
+        <v>6818</v>
       </c>
       <c r="I173" t="n">
-        <v>105500.21</v>
+        <v>19890.69</v>
       </c>
       <c r="J173" t="n">
-        <v>31650.06</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>73850.14999999999</v>
+        <v>19890.69</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>7/24 SLA Destek &amp; Bakım Sözleşmesi</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E174" t="n">
-        <v>4200</v>
+        <v>28000</v>
       </c>
       <c r="F174" t="n">
-        <v>94041.39</v>
+        <v>22726.68</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>673.67</v>
       </c>
       <c r="H174" t="n">
-        <v>62694.26</v>
+        <v>7710.84</v>
       </c>
       <c r="I174" t="n">
-        <v>94041.39</v>
+        <v>22053.01</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>11026.5</v>
       </c>
       <c r="K174" t="n">
-        <v>94041.39</v>
+        <v>11026.51</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E175" t="n">
-        <v>8900</v>
+        <v>48000</v>
       </c>
       <c r="F175" t="n">
-        <v>211000.42</v>
+        <v>101296.06</v>
       </c>
       <c r="G175" t="n">
-        <v>3978.93</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>139876.68</v>
+        <v>33765.35</v>
       </c>
       <c r="I175" t="n">
-        <v>207021.49</v>
+        <v>101296.06</v>
       </c>
       <c r="J175" t="n">
-        <v>62106.45</v>
+        <v>50648.03</v>
       </c>
       <c r="K175" t="n">
-        <v>144915.04</v>
+        <v>50648.03</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu B - Nova</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E176" t="n">
-        <v>4200</v>
+        <v>125000</v>
       </c>
       <c r="F176" t="n">
-        <v>55318.46</v>
+        <v>223208.47</v>
       </c>
       <c r="G176" t="n">
-        <v>1564.75</v>
+        <v>4410.92</v>
       </c>
       <c r="H176" t="n">
-        <v>36878.97</v>
+        <v>74998.05</v>
       </c>
       <c r="I176" t="n">
-        <v>53753.71</v>
+        <v>218797.55</v>
       </c>
       <c r="J176" t="n">
-        <v>26876.85</v>
+        <v>109398.77</v>
       </c>
       <c r="K176" t="n">
-        <v>26876.86</v>
+        <v>109398.78</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Nova</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Cloud Altyapı &amp; DevOps Yönetimi</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E177" t="n">
-        <v>1200</v>
+        <v>48000</v>
       </c>
       <c r="F177" t="n">
-        <v>3161.05</v>
+        <v>101296.06</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>2160.05</v>
+        <v>33765.35</v>
       </c>
       <c r="I177" t="n">
-        <v>3161.05</v>
+        <v>101296.06</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>3161.05</v>
+        <v>101296.06</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Nova</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Enterprise SaaS Yıllık Lisans</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E178" t="n">
-        <v>2400</v>
+        <v>125000</v>
       </c>
       <c r="F178" t="n">
-        <v>12644.22</v>
+        <v>344958.55</v>
       </c>
       <c r="G178" t="n">
-        <v>357.66</v>
+        <v>17042.2</v>
       </c>
       <c r="H178" t="n">
-        <v>7902.64</v>
+        <v>115906.07</v>
       </c>
       <c r="I178" t="n">
-        <v>12286.56</v>
+        <v>327916.35</v>
       </c>
       <c r="J178" t="n">
-        <v>3685.97</v>
+        <v>163958.17</v>
       </c>
       <c r="K178" t="n">
-        <v>8600.59</v>
+        <v>163958.18</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu A - Nova</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E179" t="n">
-        <v>1850</v>
+        <v>65000</v>
       </c>
       <c r="F179" t="n">
-        <v>24366.47</v>
+        <v>63310.04</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1876.65</v>
       </c>
       <c r="H179" t="n">
-        <v>16463.83</v>
+        <v>21428.01</v>
       </c>
       <c r="I179" t="n">
-        <v>24366.47</v>
+        <v>61433.39</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
+        <v>18430.02</v>
       </c>
       <c r="K179" t="n">
-        <v>24366.47</v>
+        <v>43003.37</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toptan Müşteri F - Nova</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Mikroservis Mimari Danışmanlığı</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E180" t="n">
-        <v>1850</v>
+        <v>90000</v>
       </c>
       <c r="F180" t="n">
-        <v>56042.87</v>
+        <v>102270.06</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>37866.8</v>
+        <v>35226.36</v>
       </c>
       <c r="I180" t="n">
-        <v>56042.87</v>
+        <v>102270.06</v>
       </c>
       <c r="J180" t="n">
-        <v>16812.86</v>
+        <v>30681.02</v>
       </c>
       <c r="K180" t="n">
-        <v>39230.01</v>
+        <v>71589.03999999999</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - Nova</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kurumsal Veri Güvenliği Denetimi</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E181" t="n">
-        <v>1850</v>
+        <v>65000</v>
       </c>
       <c r="F181" t="n">
-        <v>14619.88</v>
+        <v>158275.1</v>
       </c>
       <c r="G181" t="n">
-        <v>413.54</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>9878.299999999999</v>
+        <v>53570.03</v>
       </c>
       <c r="I181" t="n">
-        <v>14206.34</v>
+        <v>158275.1</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>79137.55</v>
       </c>
       <c r="K181" t="n">
-        <v>14206.34</v>
+        <v>79137.55</v>
       </c>
     </row>
   </sheetData>
